--- a/data/manual/j40-master-tracker.xlsx
+++ b/data/manual/j40-master-tracker.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase of Services" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Purchase of Services'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-12 22:32:10</t>
+          <t>2026-05-01 00:56:09</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>121103</v>
+        <v>93093</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>16000</v>
+        <v>69397</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -747,20 +747,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -823,12 +823,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>7860</v>
+        <v>4999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -846,44 +846,44 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>quoted_initial</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quote_hot_rod_wiring</t>
+          <t>part_dielectric_grease</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hot rod wiring quote</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>28010</v>
+        <v>5609</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -901,44 +901,44 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>quoted_initial</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>akber_khan-00494</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>part_electric_wires</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New battery purchase</t>
+          <t>Electric wires</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>20000</v>
+        <v>11529</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -971,29 +971,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received_candidate</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quote_pet_braided_sleeving</t>
+          <t>tool_electrical_test_kit</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>7414</v>
+        <v>8811</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>quoted_initial</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>electronicsstore.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,24 +1031,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quote_universal_21_circuit_kit</t>
+          <t>quote_rubber_grommet_set_chat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Universal 21-circuit wiring kit quote</t>
+          <t>Electrical wire grommet set (200pcs)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>43570</v>
+        <v>7860</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1086,24 +1086,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>akber_khan-00495</t>
+          <t>fj40-00276</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quote_wiring_harness</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wiring harness quote</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>34249</v>
+        <v>3250</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1121,53 +1121,53 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>quoted_initial</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>akber_khan-00493</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
+          <t>part_h4_ceramic_headlight_connector_high</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>H4 Ceramic Headlight Connector - H4 - High</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>11365</v>
+        <v>1350</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1176,92 +1176,587 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>quote_hot_rod_wiring</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hot rod wiring quote</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>28010</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>registered_purchase</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>akber_khan-00494|user_update_2026-04-22_wiring_built</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>part_old_man_emu_shocks</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>575000</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ironman 4x4 supplier</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>part_battery_purchase</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>New battery purchase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>registered_purchase</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ghazi Road</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>akber_khan-00753</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2188</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daraz</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>quote_pet_braided_sleeving</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7414</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>quoted_initial</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>electronicsstore.pk</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fj40-00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Seam sealer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7696</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quote_universal_21_circuit_kit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Universal 21-circuit wiring kit quote</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>43570</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>quoted_initial</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>akber_khan-00495</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>quote_wiring_harness</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wiring harness quote</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>34249</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>quoted_initial</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>akber_khan-00493</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>admin_excise_challan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Excise challan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>11365</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>registered_purchase</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fj40 group</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fj40-00025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>admin_vehicle_inspection</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Vehicle inspection</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>services</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D18" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>registered_purchase</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Fj40 group</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>needs_confirmation</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>fj40-00025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:K18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1272,12 +1767,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -1360,17 +1855,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New battery purchase</t>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1390,16 +1885,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I2" s="5" t="n">
-        <v>20000</v>
+        <v>4999</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1408,34 +1903,30 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Gross battery purchase amount before the old-battery return credit</t>
+          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
+          <t>part_dielectric_grease</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1450,21 +1941,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>received</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>-4000</v>
+        <v>5609</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1473,39 +1964,39 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>akber_khan-00760</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Return value received against the old battery; offsets battery replacement cost</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx. Gmail AliExpress evidence shows dielectric grease order 3070231697777489 shipped and package PK001206015RS delivered.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1520,16 +2011,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>11365</v>
+        <v>3250</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1538,39 +2029,39 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Vehicle transfer cost mentioned in the group chat</t>
+          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>admin_vehicle_purchase</t>
+          <t>part_battery_purchase</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vehicle purchase price</t>
+          <t>New battery purchase</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1585,15 +2076,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" s="5" t="n">
+        <v>20000</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -1601,30 +2094,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>fj40-00014</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
+          <t>Gross battery purchase amount before the old-battery return credit</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tool_bench_grinder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>credit_old_battery_return</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bench grinder</t>
+          <t>Old battery return credit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1634,25 +2131,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>received</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>-4000</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -1660,30 +2159,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>akber_khan-00760</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Seeded as received; a later tool basket shows an Ingco Bench Grinder 350w BG83502 at Rs.21,170 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
+          <t>Return value received against the old battery; offsets battery replacement cost</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_cable_sleeve_protection</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cable sleeve protection</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1693,12 +2196,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1719,58 +2222,64 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / HAQ ELECTRIC</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Seeded as received; later chat baskets show braided sleeving and heatproof sleeve options under consideration Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tool_cover</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>admin_excise_challan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Excise challan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>received</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>11365</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -1778,55 +2287,59 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
+          <t>Vehicle transfer cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>admin_vehicle_purchase</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Vehicle purchase price</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1837,30 +2350,30 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>fj40-00014</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_dielectric_grease</t>
+          <t>part_mech_air_filter</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dielectric grease</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1896,30 +2409,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Adenwalla &amp; Sons</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
+          <t>part_cable_sleeve_protection</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Cable sleeve protection</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1939,12 +2452,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1955,30 +2468,30 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Allied Electronics (confirm)</t>
+          <t>electronicsstore.pk / HAQ ELECTRIC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638</t>
+          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>User thinks this may already have been ordered; hold here until email or invoice proof confirms the exact item and price Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Seeded as received; later chat baskets show braided sleeving and heatproof sleeve options under consideration Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
+          <t>tool_cover</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2014,30 +2527,30 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
+          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
+          <t>part_copper_grease</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,7 +2586,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2083,20 +2596,24 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Listed with Y in the user purchase list</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>part_electric_wires</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Electric wires</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2111,7 +2628,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2121,10 +2638,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>received</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>received_candidate</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>11529</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2132,30 +2651,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; tap set was later discussed as useful for stripped bolts Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>User reports most electrical is already built; verify any remaining cable-length gaps physically before buying more wire Vendor backfilled from J40_Costs.xlsx. Gmail AliExpress confirms silicone cable red/black wire 1m 4AWG (order 3070027285627489) and package PK015187314R delivered on 2026-03-30.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>part_evaporust_5l</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2191,39 +2714,35 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; torque wrench was explicitly called out in tool planning chat Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>admin_vehicle_inspection</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>tool_grease_gun</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vehicle inspection</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2233,22 +2752,20 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>5000</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2256,34 +2773,34 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Inspection cost mentioned in the group chat</t>
+          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
+          <t>part_h4_ceramic_headlight_connector_high</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
+          <t>H4 Ceramic Headlight Connector - H4 - High</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2293,26 +2810,26 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>7860</v>
+        <v>1350</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2321,34 +2838,30 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Quoted in chat as part of the electrical materials basket Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; aligns with the H4-style headlight upgrade direction already captured in the design spec. Gmail shows Auto Xpert order 1599 for this exact item and workbook Parts row 76 is marked received Y and paid Y so this remains in needs confirmation pending final reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quote_hot_rod_wiring</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>part_hidden_diesel_cutoff_switch</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hot rod wiring quote</t>
+          <t>Hidden diesel cutoff switch (binary toggle)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2358,27 +2871,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>28010</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2386,34 +2897,34 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>akber_khan-00494</t>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Selected as the baseline electrical starting point because it is the lowest-cost labeled 21-circuit kit among the current candidates and still gives enough headroom for the J40 baseline circuits</t>
+          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>quote_pet_braided_sleeving</t>
+          <t>quote_hot_rod_wiring</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
+          <t>Hot rod wiring quote</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2423,26 +2934,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>7414</v>
+        <v>28010</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2451,34 +2962,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>electronicsstore.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>akber_khan-00494|user_update_2026-04-22_wiring_built</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Quoted in chat as part of the electrical materials basket Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>User reports this wiring path was already executed and the vehicle is wired up; treat this quote as fulfilled and closed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>quote_universal_21_circuit_kit</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>part_piano_hinge</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Universal 21-circuit wiring kit quote</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2488,27 +2995,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>43570</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2516,34 +3021,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>akber_khan-00495</t>
+          <t>user_seed</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Held as an alternative reference after the baseline electrical starting point was narrowed to the lower-cost hot rod harness path</t>
+          <t>Listed with Y in the user purchase list</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>quote_wiring_harness</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>tool_tap_set</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wiring harness quote</t>
+          <t>Tap set</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2553,27 +3054,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>34249</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2581,30 +3080,30 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>akber_khan-00493</t>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Held as an alternative reference after the baseline electrical starting point was narrowed to the lower-cost hot rod harness path</t>
+          <t>Marked with x in the user purchase list; tap set was later discussed as useful for stripped bolts Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tool_breaker_bar</t>
+          <t>part_mech_thermostat_gasket</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1/2 inch 24 inch breaker bar, heavy duty</t>
+          <t>Thermostat plus gasket</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2614,22 +3113,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2640,30 +3139,30 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00346</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; breaker bar was part of the minimum tool list discussed around steering work</t>
+          <t>Marked received per user confirmation; compatibility/usability can be validated during install planning</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>part_mech_accessory_belt_set</t>
+          <t>tool_torque_wrench</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accessory belt set</t>
+          <t>Torque wrench</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2673,22 +3172,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2699,58 +3198,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00395</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Marked with x in the user purchase list; torque wrench was explicitly called out in tool planning chat Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>admin_vehicle_inspection</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Vehicle inspection</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>5000</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2758,30 +3263,34 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Inspection cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>part_android_unit</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>quote_rubber_grommet_set_chat</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Android unit</t>
+          <t>Electrical wire grommet set (200pcs)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2791,7 +3300,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2809,7 +3318,9 @@
           <t>deferred_optional</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" s="5" t="n">
+        <v>7860</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2817,30 +3328,34 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SehgalMotors.PK</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
+          <t>fj40-00276</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9 inch, flush-mounted, integrated into the dash panel; later shopping basket includes a priced Android unit candidate Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Reference quote only; duplicate path now superseded by the received AliExpress grommet set Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>part_bed_lining</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>quote_pet_braided_sleeving</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bed lining</t>
+          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2850,7 +3365,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2865,10 +3380,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>7414</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2876,30 +3393,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
+          <t>fj40-00276</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat sequences this after welding/primer and before sound deadening</t>
+          <t>Quoted in chat as part of the electrical materials basket Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>part_bedliner_sprays</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>quote_universal_21_circuit_kit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bedliner sprays</t>
+          <t>Universal 21-circuit wiring kit quote</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2909,7 +3430,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2924,10 +3445,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>43570</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2935,30 +3458,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
+          <t>akber_khan-00495</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat says they are required immediately after floor repair and primer</t>
+          <t>Held as an alternative reference after the baseline electrical starting point was narrowed to the lower-cost hot rod harness path</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>quote_wiring_harness</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Wiring harness quote</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2968,7 +3495,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2983,10 +3510,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>34249</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2994,30 +3523,30 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>akber_khan-00493</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>MECH SAFETY MUST REPLACE during full restore before final road validation</t>
+          <t>Held as an alternative reference after the baseline electrical starting point was narrowed to the lower-cost hot rod harness path</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>part_carpet</t>
+          <t>tool_breaker_bar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carpet</t>
+          <t>1/2 inch 24 inch breaker bar, heavy duty</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3042,7 +3571,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3053,30 +3582,30 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00346</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>Listed by the user as still needed; breaker bar was part of the minimum tool list discussed around steering work</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>part_mech_clutch_master_slave_refresh</t>
+          <t>part_mech_accessory_belt_set</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Clutch master and slave cylinder refresh kit</t>
+          <t>Accessory belt set</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3101,7 +3630,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3122,20 +3651,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>MECH INSPECT THEN REPLACE if leakage pedal sink or seized seals</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
+          <t>part_firewall_grommet_set_large_power</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3176,25 +3705,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore if distributor ignition remains</t>
+          <t>Large pass-through sizes still needed for protected heavy feed runs and split-loom trunk crossings</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>part_electric_wires</t>
+          <t>part_firewall_grommet_set_small_medium</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Electric wires</t>
+          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3230,30 +3759,30 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat explicitly calls out starter, alternator, and accessory cable additions Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Additional small and medium pass-through sizes still needed to cover loom branch and signal wire firewall exits</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>part_mech_engine_mount_set</t>
+          <t>part_android_unit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Engine mount set</t>
+          <t>Android unit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3278,7 +3807,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3289,30 +3818,30 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>SehgalMotors.PK</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
+          <t>9 inch, flush-mounted, integrated into the dash panel; later shopping basket includes a priced Android unit candidate Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>part_mech_engine_oil_filter_service</t>
+          <t>part_bed_lining</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Engine oil + oil filter service pack</t>
+          <t>Bed lining</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3337,7 +3866,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3353,25 +3882,25 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Listed by the user as still needed; chat sequences this after welding/primer and before sound deadening</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
+          <t>part_bedliner_sprays</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Bedliner sprays</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3396,7 +3925,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3412,25 +3941,25 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; chat says they are required immediately after floor repair and primer</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>part_foam</t>
+          <t>part_body_mount_hardware_kit</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Body mount hardware kit bolts sleeves washers</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3455,7 +3984,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -3471,25 +4000,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>New graded hardware required for reliable tub refit</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
+          <t>part_body_mount_shim_pack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
+          <t>Body mount shim and spacer pack</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3530,25 +4059,25 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Shim set needed for mount alignment during trial fit</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
+          <t>part_body_mount_rubber_kit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Body-to-chassis mount rubber kit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3589,25 +4118,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE old soft fuel lines during full restore</t>
+          <t>Replace all tub mounts before final body refit torque</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>part_h4_ceramic_headlight_connector_high</t>
+          <t>part_mech_brake_flex_hose_set</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>H4 Ceramic Headlight Connector - H4 - High</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3648,25 +4177,25 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; aligns with the H4-style headlight upgrade direction already captured in the design spec</t>
+          <t>MECH SAFETY MUST REPLACE during full restore before final road validation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
+          <t>part_carpet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Carpet</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3691,7 +4220,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -3707,25 +4236,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
+          <t>part_mech_clutch_master_slave_refresh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Clutch master and slave cylinder refresh kit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3750,7 +4279,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -3766,25 +4295,25 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
+          <t>MECH INSPECT THEN REPLACE if leakage pedal sink or seized seals</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3820,30 +4349,34 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
+          <t>MECH BASELINE MUST REPLACE during full restore if distributor ignition remains</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_primer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>tool_electrical_test_kit</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3868,10 +4401,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>8811</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3879,30 +4414,30 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
+          <t>User update 2026-04-27: no reliable order evidence for ANENG ST170 test kit; keep as unconfirmed/not ordered until explicit proof is found.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
+          <t>part_mech_engine_mount_set</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Engine mount set</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3927,7 +4462,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -3948,20 +4483,20 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
+          <t>part_mech_engine_oil_filter_service</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Engine oil + oil filter service pack</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4014,13 +4549,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
+          <t>part_epoxy_primer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4056,30 +4591,30 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_foam</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4104,7 +4639,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -4125,20 +4660,20 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_mech_fuel_filter</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4163,7 +4698,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -4179,25 +4714,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_mech_fuel_hose_and_clamps</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4243,20 +4778,20 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>MECH BASELINE MUST REPLACE old soft fuel lines during full restore</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
+          <t>part_mech_heater_hose_set</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Large</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4297,25 +4832,25 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; large-diameter wire protection still needed as a distinct line item</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
+          <t>part_horn_relay</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Medium</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4361,20 +4896,20 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; medium-diameter wire protection still needed as a distinct line item</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_metal_protection</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Small</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4410,30 +4945,30 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; small-diameter wire protection still needed as a distinct line item</t>
+          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>part_primer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4458,7 +4993,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -4474,25 +5009,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch</t>
+          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4533,25 +5068,25 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4604,13 +5139,13 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_toggle_switch</t>
+          <t>part_self_etching_primer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4651,25 +5186,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; function-specific switch to lock once the control layout is finalized</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4694,7 +5229,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -4710,25 +5245,25 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE old brittle vacuum lines during full restore</t>
+          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>part_mech_spark_plugs_set</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Spark plugs set</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4753,7 +5288,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -4764,30 +5299,30 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>Split conduit / braided sleeve - Large</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4812,7 +5347,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -4833,20 +5368,20 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; large-diameter wire protection still needed as a distinct line item</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>part_wiring_kit</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wiring kit</t>
+          <t>Split conduit / braided sleeve - Medium</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4871,7 +5406,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -4882,30 +5417,30 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00493|akber_khan-00494|akber_khan-00495</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Generic requirement row only; the active baseline buy path is now the selected hot rod harness quote rather than an extra separate wiring-kit purchase Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; medium-diameter wire protection still needed as a distinct line item</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_bilstein_shocks</t>
+          <t>part_split_conduit_braided_sleeve_small</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bilstein 5100 / 5160 shocks</t>
+          <t>Split conduit / braided sleeve - Small</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4915,7 +5450,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4925,12 +5460,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -4946,25 +5481,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00857|akber_khan-00858</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Suspension option under consideration</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; small-diameter wire protection still needed as a distinct line item</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>part_old_man_emu_shocks</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Old Man Emu Nitrocharger</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4974,7 +5509,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4984,12 +5519,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -5005,25 +5540,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00857|akber_khan-00858</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Suspension option under consideration</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5033,7 +5568,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5043,12 +5578,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -5064,25 +5599,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
+          <t>part_mech_vacuum_hose_refresh</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Vacuum hose refresh kit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5092,22 +5627,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -5118,22 +5653,575 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>MECH BASELINE MUST REPLACE old brittle vacuum lines during full restore</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>part_wax_and_grease_remover</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Wax and grease remover</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>part_winch_switch</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Winch switch</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>deferred_optional</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>part_wiring_kit</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wiring kit</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>deferred_optional</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>User directly confirmed this was ordered; exact product link: https://www.aliexpress.com/i/1005008318051049.html</t>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00489|akber_khan-00493|akber_khan-00494|akber_khan-00495|user_update_2026-04-22_wiring_built</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Superseded for now because user reports wiring is already built; reopen only if later rewire scope is identified Vendor backfilled from J40_Costs.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>part_power_steering_upgrade</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Power steering upgrade</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>tool_bench_grinder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bench grinder</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>deferred_optional</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Toolsmart</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>User update 2026-04-27: bench grinder currently considered not required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>part_ironman_front_dampers_separate_shipment</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ironman 4x4 supplier</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Bifurcated shipment tracker for the front damper pair arriving separately from the rest of the Ironman kit. Amount is included in the main Ironman kit total to avoid double-counting. Verify 24635FE x2 on receipt before closing suspension procurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>part_old_man_emu_shocks</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>575000</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Ironman 4x4 supplier</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>User update 2026-05-01: Ironman Foamcell suspension kit ordered from attached parts list; PKR 600000 less PKR 25000 discount = PKR 575000 total. Track as main shipment plus a separate front damper shipment. Supplier list shows part numbers 24635FE, 24636FE, TOY001B, TOY002B, 415UBK, 713UK, 343LH, 343RH, 3523, 346. All previous local spring, OME/Bilstein, separate bushing, shackle, and U-bolt alternatives removed from active parts list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>2188</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Daraz</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>User update: 2 sets purchased and paid; not yet received Gmail Daraz confirmation matched exact item + quantity (2) and total PKR 2188; ETA 2026-04-27..2026-04-29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Seam sealer</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>7696</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link. Gmail Autohub order 1761310 confirms 3x HB BODY 999 seam sealer and shipment status.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M64"/>
+  <autoFilter ref="A1:M73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5144,12 +6232,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -5342,13 +6430,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
+          <t>part_firewall_grommet_set_large_power</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5390,20 +6478,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>part_android_unit</t>
+          <t>part_firewall_grommet_set_small_medium</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Android unit</t>
+          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5435,37 +6523,37 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SehgalMotors.PK</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>part_bed_lining</t>
+          <t>part_mech_air_filter</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bed lining</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5475,22 +6563,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -5500,20 +6588,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_bedliner_sprays</t>
+          <t>part_android_unit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bedliner sprays</t>
+          <t>Android unit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5545,37 +6633,37 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>SehgalMotors.PK</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
+          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tool_bench_grinder</t>
+          <t>part_bed_lining</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bench grinder</t>
+          <t>Bed lining</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5585,52 +6673,52 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>part_bilstein_shocks</t>
+          <t>part_bedliner_sprays</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bilstein 5100 / 5160 shocks</t>
+          <t>Bedliner sprays</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5640,7 +6728,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5650,12 +6738,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -5665,27 +6753,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00857|akber_khan-00858</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
+          <t>tool_bench_grinder</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Bench grinder</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5695,7 +6783,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5705,42 +6793,42 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_cable_sleeve_protection</t>
+          <t>part_body_mount_hardware_kit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cable sleeve protection</t>
+          <t>Body mount hardware kit bolts sleeves washers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5750,52 +6838,52 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / HAQ ELECTRIC</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tool_cover</t>
+          <t>part_body_mount_shim_pack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Body mount shim and spacer pack</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5805,45 +6893,45 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_carpet</t>
+          <t>part_body_mount_rubber_kit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carpet</t>
+          <t>Body-to-chassis mount rubber kit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -5875,7 +6963,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5885,20 +6973,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>part_mech_clutch_master_slave_refresh</t>
+          <t>part_mech_brake_flex_hose_set</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Clutch master and slave cylinder refresh kit</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5930,7 +7018,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -5947,13 +7035,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
+          <t>part_cable_sleeve_protection</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Cable sleeve protection</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5990,25 +7078,25 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>electronicsstore.pk / HAQ ELECTRIC</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>part_dielectric_grease</t>
+          <t>tool_cover</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dielectric grease</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -6045,25 +7133,25 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Adenwalla &amp; Sons</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
+          <t>part_carpet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>Carpet</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6095,7 +7183,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -6105,20 +7193,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>part_electric_wires</t>
+          <t>part_mech_clutch_master_slave_refresh</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Electric wires</t>
+          <t>Clutch master and slave cylinder refresh kit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -6150,37 +7238,37 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
+          <t>part_copper_grease</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6200,48 +7288,48 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Allied Electronics (confirm)</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>7860</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" s="5" t="n">
+        <v>4999</v>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6251,100 +7339,102 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>part_mech_engine_mount_set</t>
+          <t>part_dielectric_grease</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Engine mount set</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>5609</v>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>part_mech_engine_oil_filter_service</t>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Engine oil + oil filter service pack</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -6393,72 +7483,84 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>part_electric_wires</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Electric wires</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>11529</v>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received_candidate</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>part_foam</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>tool_electrical_test_kit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>8811</v>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>planned</t>
@@ -6466,7 +7568,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6486,47 +7588,53 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>quote_rubber_grommet_set_chat</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Electrical wire grommet set (200pcs)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>7860</v>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6541,30 +7649,30 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>fj40-00276</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
+          <t>part_mech_engine_mount_set</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Engine mount set</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -6596,7 +7704,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -6613,20 +7721,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
+          <t>part_mech_engine_oil_filter_service</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Engine oil + oil filter service pack</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -6636,45 +7744,45 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>part_h4_ceramic_headlight_connector_high</t>
+          <t>part_epoxy_primer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>H4 Ceramic Headlight Connector - H4 - High</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -6706,7 +7814,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -6716,27 +7824,31 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>part_evaporust_5l</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -6746,45 +7858,45 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
+          <t>part_foam</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6816,7 +7928,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -6826,43 +7938,37 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>quote_hot_rod_wiring</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>part_mech_fuel_filter</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hot rod wiring quote</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>28010</v>
-      </c>
+          <t>Fuel filter</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -6882,25 +7988,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>akber_khan-00494</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
+          <t>part_mech_fuel_hose_and_clamps</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6937,38 +8043,38 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New battery purchase</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>20000</v>
+        <v>3250</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -6988,42 +8094,42 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>part_old_man_emu_shocks</t>
+          <t>tool_grease_gun</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Old Man Emu Nitrocharger</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7033,56 +8139,58 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00857|akber_khan-00858</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
+          <t>part_h4_ceramic_headlight_connector_high</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>H4 Ceramic Headlight Connector - H4 - High</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>1350</v>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>credited</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7092,68 +8200,62 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>akber_khan-00760</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>quote_pet_braided_sleeving</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
+          <t>part_mech_heater_hose_set</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>7414</v>
-      </c>
+          <t>Heater hose set with clamps</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -7173,25 +8275,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>electronicsstore.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
+          <t>part_hidden_diesel_cutoff_switch</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Hidden diesel cutoff switch (binary toggle)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -7233,27 +8335,27 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
+          <t>part_horn_relay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7263,7 +8365,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -7273,12 +8375,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -7288,82 +8390,92 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>part_primer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>quote_hot_rod_wiring</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Hot rod wiring quote</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>28010</v>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>akber_khan-00494|user_update_2026-04-22_wiring_built</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>part_ironman_front_dampers_separate_shipment</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7373,107 +8485,113 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>part_old_man_emu_shocks</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" s="5" t="n">
+        <v>575000</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
+          <t>part_metal_protection</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7483,227 +8601,249 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>part_battery_purchase</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>New battery purchase</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>20000</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
+        <v>2188</v>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>credit_old_battery_return</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Old battery return credit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>credited</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>akber_khan-00760</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>quote_pet_braided_sleeving</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>7414</v>
+      </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -7723,32 +8863,32 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>fj40-00276</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
+          <t>part_piano_hinge</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Large</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7758,22 +8898,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -7783,27 +8923,27 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
+          <t>part_power_steering_upgrade</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Medium</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7813,7 +8953,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -7823,12 +8963,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7838,20 +8978,20 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_primer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Small</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -7893,20 +9033,20 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -7938,7 +9078,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -7948,20 +9088,20 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -8003,20 +9143,24 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -8033,12 +9177,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -8053,80 +9197,86 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>7696</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_toggle_switch</t>
+          <t>part_self_etching_primer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -8168,27 +9318,27 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8198,68 +9348,62 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>quote_universal_21_circuit_kit</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>part_mech_spark_plugs_set</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Universal 21-circuit wiring kit quote</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>43570</v>
-      </c>
+          <t>Spark plugs set</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -8274,30 +9418,30 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>akber_khan-00495</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Split conduit / braided sleeve - Large</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -8339,20 +9483,20 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Split conduit / braided sleeve - Medium</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -8384,30 +9528,30 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
+          <t>part_split_conduit_braided_sleeve_small</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>Split conduit / braided sleeve - Small</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -8439,7 +9583,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -8456,36 +9600,30 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>quote_wiring_harness</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>part_spotlight_switch</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wiring harness quote</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>34249</v>
-      </c>
+          <t>Spotlight switch</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -8500,30 +9638,30 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>akber_khan-00493</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_wiring_kit</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wiring kit</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -8555,22 +9693,529 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>tool_tap_set</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tap set</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ToolsMart.pk</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>part_mech_thermostat_gasket</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Thermostat plus gasket</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>tool_torque_wrench</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Torque wrench</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>ToolsMart.pk</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00395</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>quote_universal_21_circuit_kit</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Universal 21-circuit wiring kit quote</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>43570</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>quote_only</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>researching</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00493|akber_khan-00494|akber_khan-00495</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>akber_khan-00495</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>part_mech_vacuum_hose_refresh</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Vacuum hose refresh kit</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>part_wax_and_grease_remover</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wax and grease remover</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>part_winch_switch</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Winch switch</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>deferred_optional</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>quote_wiring_harness</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wiring harness quote</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>34249</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>quote_only</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>researching</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>akber_khan-00493</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>part_wiring_kit</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wiring kit</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>deferred_optional</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00489|akber_khan-00493|akber_khan-00494|akber_khan-00495|user_update_2026-04-22_wiring_built</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M61"/>
+  <autoFilter ref="A1:M70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/manual/j40-master-tracker.xlsx
+++ b/data/manual/j40-master-tracker.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-01 00:56:09</t>
+          <t>2026-05-01 01:07:05</t>
         </is>
       </c>
     </row>

--- a/data/manual/j40-master-tracker.xlsx
+++ b/data/manual/j40-master-tracker.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase of Services" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Purchase of Services'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-01 01:07:05</t>
+          <t>2026-05-01 01:41:30</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>93093</v>
+        <v>7860</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>69397</v>
+        <v>42737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electric wires</t>
+          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>received_candidate</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H4 Ceramic Headlight Connector - H4 - High</t>
+          <t>H4 ceramic headlight connectors - x4 received</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quote_hot_rod_wiring</t>
+          <t>part_ironman_foamcell_suspension_kit</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hot rod wiring quote</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>28010</v>
+        <v>575000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1246,29 +1246,29 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>akber_khan-00494|user_update_2026-04-22_wiring_built</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_old_man_emu_shocks</t>
+          <t>part_battery_purchase</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>575000</v>
+        <v>20000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1286,44 +1286,44 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New battery purchase</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>20000</v>
+        <v>2188</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>part_seam_sealer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2188</v>
+        <v>7696</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1421,28 +1421,28 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>quote_pet_braided_sleeving</t>
+          <t>admin_excise_challan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
+          <t>Excise challan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>7414</v>
+        <v>11365</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1451,53 +1451,53 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>quoted_initial</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>electronicsstore.pk</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>fj40-00025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
+          <t>admin_vehicle_inspection</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Vehicle inspection</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>7696</v>
+        <v>5000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1506,257 +1506,37 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>quote_universal_21_circuit_kit</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Universal 21-circuit wiring kit quote</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>goods</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>43570</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>quoted_initial</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AliExpress</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>akber_khan-00495</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>quote_wiring_harness</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Wiring harness quote</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>goods</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>34249</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>quoted_initial</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AliExpress</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>akber_khan-00493</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>admin_excise_challan</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Excise challan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>services</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>11365</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>registered_purchase</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Fj40 group</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
           <t>fj40-00025</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>admin_vehicle_inspection</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Vehicle inspection</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>services</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>registered_purchase</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Fj40 group</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fj40-00025</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1767,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1780,7 +1560,7 @@
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
     <col width="70" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1855,17 +1635,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>part_autohub_diss_apc_cleaner_5l</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>part_cable_sleeve_protection</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DISS (APC) All Purpose Cleaner 5L</t>
+          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1893,9 +1669,7 @@
           <t>received</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
-        <v>4999</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -1903,30 +1677,34 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>electronicsstore.pk / HAQ ELECTRIC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
+          <t>Workbook inventory shows braided sleeve stock already received/paid: 8, 10, 14, 16, and 20 mm sleeve entries in 5m lengths. Audit physical quantities before any top-up.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>part_dielectric_grease</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dielectric grease</t>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1955,7 +1733,7 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>5609</v>
+        <v>4999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1964,34 +1742,30 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Adenwalla &amp; Sons</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx. Gmail AliExpress evidence shows dielectric grease order 3070231697777489 shipped and package PK001206015RS delivered.</t>
+          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>part_dielectric_grease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2020,7 +1794,7 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>3250</v>
+        <v>5609</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2029,34 +1803,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx. Gmail AliExpress evidence shows dielectric grease order 3070231697777489 shipped and package PK001206015RS delivered.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>part_electric_wires</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New battery purchase</t>
+          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2076,16 +1850,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>20000</v>
+        <v>11529</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2094,34 +1868,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Gross battery purchase amount before the old-battery return credit</t>
+          <t>Received AliExpress order 3070027285627489: 4 AWG silicone cable, red/black, 1m each (approx 21 mm2). Workbook also contains 1.0/1.5/2.5 mm2 roll inventory; physically count before buying more wire.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2136,21 +1910,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>-4000</v>
+        <v>3250</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2159,34 +1933,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>akber_khan-00760</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Return value received against the old battery; offsets battery replacement cost</t>
+          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
+          <t>part_h4_ceramic_headlight_connector_high</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>H4 ceramic headlight connectors - x4 received</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2214,7 +1988,9 @@
           <t>received</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" s="5" t="n">
+        <v>1350</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2222,39 +1998,39 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html</t>
+          <t>User has 4 H4 ceramic headlight connectors received. Only 2 are required for the headlights, leaving 2 spares; no additional H4 connectors are required.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
+          <t>part_battery_purchase</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2269,16 +2045,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
       <c r="I8" s="5" t="n">
-        <v>11365</v>
+        <v>20000</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2287,39 +2063,39 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Vehicle transfer cost mentioned in the group chat</t>
+          <t>New battery is already purchased and installed. Gross PKR 20,000 before old-battery return credit.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>admin_vehicle_purchase</t>
+          <t>credit_old_battery_return</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vehicle purchase price</t>
+          <t>Old battery return credit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2329,7 +2105,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2342,7 +2118,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" s="5" t="n">
+        <v>-4000</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2350,30 +2128,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>fj40-00014</t>
+          <t>akber_khan-00760</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
+          <t>PKR 4,000 return value received against the old battery; net new-battery cost is PKR 16,000.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2383,12 +2165,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2409,30 +2191,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
+          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_cable_sleeve_protection</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cable sleeve protection</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2442,12 +2224,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2468,30 +2250,30 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / HAQ ELECTRIC</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Seeded as received; later chat baskets show braided sleeving and heatproof sleeve options under consideration Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Covered by received workbook sleeve inventory (14mm and 16mm, 5m lengths). No additional medium sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tool_cover</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2501,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2527,30 +2309,30 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
+          <t>Covered by received workbook sleeve inventory (20mm, 5m lengths). No additional large sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
+          <t>part_split_conduit_braided_sleeve_small</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2560,12 +2342,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2586,44 +2368,44 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Covered by received workbook sleeve inventory (8mm and 10mm, 5m lengths). No additional small sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>part_electric_wires</t>
+          <t>admin_excise_challan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Electric wires</t>
+          <t>Excise challan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2633,16 +2415,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>received_candidate</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>11529</v>
+        <v>11365</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -2651,59 +2433,59 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>User reports most electrical is already built; verify any remaining cable-length gaps physically before buying more wire Vendor backfilled from J40_Costs.xlsx. Gmail AliExpress confirms silicone cable red/black wire 1m 4AWG (order 3070027285627489) and package PK015187314R delivered on 2026-03-30.</t>
+          <t>Vehicle transfer cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>part_evaporust_5l</t>
+          <t>admin_vehicle_purchase</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
+          <t>Vehicle purchase price</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2714,30 +2496,30 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7mart</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
+          <t>fj40-00014</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
+          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
+          <t>part_mech_air_filter</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2773,34 +2555,30 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
+          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>part_h4_ceramic_headlight_connector_high</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>tool_cover</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>H4 Ceramic Headlight Connector - H4 - High</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2820,17 +2598,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>1350</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2838,30 +2614,30 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Auto Xpert Pakistan</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; aligns with the H4-style headlight upgrade direction already captured in the design spec. Gmail shows Auto Xpert order 1599 for this exact item and workbook Parts row 76 is marked received Y and paid Y so this remains in needs confirmation pending final reconciliation.</t>
+          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>part_hidden_diesel_cutoff_switch</t>
+          <t>part_copper_grease</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hidden diesel cutoff switch (binary toggle)</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2897,24 +2673,24 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
+          <t>user_seed</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>quote_hot_rod_wiring</t>
+          <t>part_evaporust_5l</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2924,7 +2700,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hot rod wiring quote</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2944,17 +2720,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>28010</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2962,30 +2736,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>akber_khan-00494|user_update_2026-04-22_wiring_built</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>User reports this wiring path was already executed and the vehicle is wired up; treat this quote as fulfilled and closed</t>
+          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
+          <t>tool_grease_gun</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3021,30 +2795,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Listed with Y in the user purchase list</t>
+          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
+          <t>part_hidden_diesel_cutoff_switch</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Hidden diesel cutoff switch (binary toggle)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3080,30 +2854,30 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; tap set was later discussed as useful for stripped bolts Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
+          <t>part_piano_hinge</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3144,25 +2918,25 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_seed</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Marked received per user confirmation; compatibility/usability can be validated during install planning</t>
+          <t>Listed with Y in the user purchase list</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
+          <t>tool_tap_set</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Tap set</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3203,34 +2977,30 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; torque wrench was explicitly called out in tool planning chat Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked with x in the user purchase list; tap set was later discussed as useful for stripped bolts Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>admin_vehicle_inspection</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>part_mech_thermostat_gasket</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vehicle inspection</t>
+          <t>Thermostat plus gasket</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3240,22 +3010,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>5000</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3263,34 +3031,30 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Inspection cost mentioned in the group chat</t>
+          <t>Marked received per user confirmation; compatibility/usability can be validated during install planning</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
+          <t>tool_torque_wrench</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
+          <t>Torque wrench</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3300,27 +3064,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>7860</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3328,63 +3090,63 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_seed|akber_khan-00395</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Reference quote only; duplicate path now superseded by the received AliExpress grommet set Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked with x in the user purchase list; torque wrench was explicitly called out in tool planning chat Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>quote_pet_braided_sleeving</t>
+          <t>admin_vehicle_inspection</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
+          <t>Vehicle inspection</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I26" s="5" t="n">
-        <v>7414</v>
+        <v>5000</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -3393,34 +3155,34 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>electronicsstore.pk</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Quoted in chat as part of the electrical materials basket Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Inspection cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quote_universal_21_circuit_kit</t>
+          <t>quote_rubber_grommet_set_chat</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Universal 21-circuit wiring kit quote</t>
+          <t>Electrical wire grommet set (200pcs)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3445,11 +3207,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>43570</v>
+        <v>7860</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -3458,34 +3220,30 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>akber_khan-00495</t>
+          <t>fj40-00276</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Held as an alternative reference after the baseline electrical starting point was narrowed to the lower-cost hot rod harness path</t>
+          <t>Reference quote only; duplicate path now superseded by the received AliExpress grommet set Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>quote_wiring_harness</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>tool_breaker_bar</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wiring harness quote</t>
+          <t>1/2 inch 24 inch breaker bar, heavy duty</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3495,7 +3253,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3510,12 +3268,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>34249</v>
-      </c>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3523,30 +3279,30 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>akber_khan-00493</t>
+          <t>user_seed|akber_khan-00346</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Held as an alternative reference after the baseline electrical starting point was narrowed to the lower-cost hot rod harness path</t>
+          <t>Listed by the user as still needed; breaker bar was part of the minimum tool list discussed around steering work</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tool_breaker_bar</t>
+          <t>part_mech_accessory_belt_set</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1/2 inch 24 inch breaker bar, heavy duty</t>
+          <t>Accessory belt set</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3571,7 +3327,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,30 +3338,30 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00346</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; breaker bar was part of the minimum tool list discussed around steering work</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>part_mech_accessory_belt_set</t>
+          <t>part_firewall_grommet_set_large_power</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Accessory belt set</t>
+          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3646,25 +3402,25 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Large pass-through sizes still needed for protected heavy feed runs and split-loom trunk crossings</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_large_power</t>
+          <t>part_firewall_grommet_set_small_medium</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
+          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3705,25 +3461,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Large pass-through sizes still needed for protected heavy feed runs and split-loom trunk crossings</t>
+          <t>Additional small and medium pass-through sizes still needed to cover loom branch and signal wire firewall exits</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_small_medium</t>
+          <t>part_android_unit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
+          <t>Android unit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3748,7 +3504,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3759,30 +3515,30 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>SehgalMotors.PK</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
+          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Additional small and medium pass-through sizes still needed to cover loom branch and signal wire firewall exits</t>
+          <t>9 inch, flush-mounted, integrated into the dash panel; later shopping basket includes a priced Android unit candidate Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>part_android_unit</t>
+          <t>part_bed_lining</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Android unit</t>
+          <t>Bed lining</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3807,7 +3563,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3818,30 +3574,30 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SehgalMotors.PK</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9 inch, flush-mounted, integrated into the dash panel; later shopping basket includes a priced Android unit candidate Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Listed by the user as still needed; chat sequences this after welding/primer and before sound deadening</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>part_bed_lining</t>
+          <t>part_bedliner_sprays</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bed lining</t>
+          <t>Bedliner sprays</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3866,7 +3622,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3882,25 +3638,25 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat sequences this after welding/primer and before sound deadening</t>
+          <t>Listed by the user as still needed; chat says they are required immediately after floor repair and primer</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>part_bedliner_sprays</t>
+          <t>part_body_mount_hardware_kit</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bedliner sprays</t>
+          <t>Body mount hardware kit bolts sleeves washers</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3941,25 +3697,25 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat says they are required immediately after floor repair and primer</t>
+          <t>New graded hardware required for reliable tub refit</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>part_body_mount_hardware_kit</t>
+          <t>part_body_mount_shim_pack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Body mount hardware kit bolts sleeves washers</t>
+          <t>Body mount shim and spacer pack</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4005,20 +3761,20 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>New graded hardware required for reliable tub refit</t>
+          <t>Shim set needed for mount alignment during trial fit</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>part_body_mount_shim_pack</t>
+          <t>part_body_mount_rubber_kit</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Body mount shim and spacer pack</t>
+          <t>Body-to-chassis mount rubber kit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4064,20 +3820,20 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Shim set needed for mount alignment during trial fit</t>
+          <t>Replace all tub mounts before final body refit torque</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>part_body_mount_rubber_kit</t>
+          <t>part_mech_brake_flex_hose_set</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Body-to-chassis mount rubber kit</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4118,25 +3874,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Replace all tub mounts before final body refit torque</t>
+          <t>MECH SAFETY MUST REPLACE during full restore before final road validation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
+          <t>part_carpet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Carpet</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4161,7 +3917,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4177,25 +3933,25 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>MECH SAFETY MUST REPLACE during full restore before final road validation</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_carpet</t>
+          <t>part_mech_clutch_master_slave_refresh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Carpet</t>
+          <t>Clutch master and slave cylinder refresh kit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4220,7 +3976,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4236,25 +3992,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>MECH INSPECT THEN REPLACE if leakage pedal sink or seized seals</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_mech_clutch_master_slave_refresh</t>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Clutch master and slave cylinder refresh kit</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4279,7 +4035,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4300,20 +4056,24 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>MECH INSPECT THEN REPLACE if leakage pedal sink or seized seals</t>
+          <t>MECH BASELINE MUST REPLACE during full restore if distributor ignition remains</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>tool_electrical_test_kit</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4338,10 +4098,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>8811</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -4349,34 +4111,30 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore if distributor ignition remains</t>
+          <t>User update 2026-04-27: no reliable order evidence for ANENG ST170 test kit; keep as unconfirmed/not ordered until explicit proof is found.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
+          <t>part_mech_engine_mount_set</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Engine mount set</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4404,9 +4162,7 @@
           <t>next_phase_purchase</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>8811</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -4414,30 +4170,30 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>User update 2026-04-27: no reliable order evidence for ANENG ST170 test kit; keep as unconfirmed/not ordered until explicit proof is found.</t>
+          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_mech_engine_mount_set</t>
+          <t>part_mech_engine_oil_filter_service</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Engine mount set</t>
+          <t>Engine oil + oil filter service pack</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4462,7 +4218,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4483,20 +4239,20 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_mech_engine_oil_filter_service</t>
+          <t>part_epoxy_primer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Engine oil + oil filter service pack</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4521,7 +4277,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4537,25 +4293,25 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
+          <t>part_foam</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4580,7 +4336,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4601,20 +4357,20 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_foam</t>
+          <t>part_mech_fuel_filter</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4639,7 +4395,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -4655,25 +4411,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
+          <t>part_mech_fuel_hose_and_clamps</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4719,20 +4475,20 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>MECH BASELINE MUST REPLACE old soft fuel lines during full restore</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
+          <t>part_mech_heater_hose_set</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4778,20 +4534,20 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE old soft fuel lines during full restore</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
+          <t>part_horn_relay</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4832,25 +4588,25 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
+          <t>part_metal_protection</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4886,30 +4642,30 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
+          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
+          <t>part_primer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4945,30 +4701,30 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
+          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_primer</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5009,25 +4765,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5080,13 +4836,13 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
+          <t>part_self_etching_primer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5111,7 +4867,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5127,25 +4883,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5170,7 +4926,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5186,25 +4942,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_mech_spark_plugs_set</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Spark plugs set</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5229,7 +4985,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -5245,25 +5001,25 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5288,7 +5044,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -5304,25 +5060,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Large</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5368,20 +5124,20 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; large-diameter wire protection still needed as a distinct line item</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
+          <t>part_mech_vacuum_hose_refresh</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Medium</t>
+          <t>Vacuum hose refresh kit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5422,25 +5178,25 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; medium-diameter wire protection still needed as a distinct line item</t>
+          <t>MECH BASELINE MUST REPLACE old brittle vacuum lines during full restore</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_wax_and_grease_remover</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Small</t>
+          <t>Wax and grease remover</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5465,7 +5221,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -5476,30 +5232,30 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; small-diameter wire protection still needed as a distinct line item</t>
+          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>part_winch_switch</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Winch switch</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5524,7 +5280,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -5545,20 +5301,20 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_power_steering_upgrade</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5568,7 +5324,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5578,12 +5334,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -5599,25 +5355,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
+          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>tool_bench_grinder</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Bench grinder</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5627,7 +5383,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5637,12 +5393,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -5653,30 +5409,34 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE old brittle vacuum lines during full restore</t>
+          <t>User update 2026-04-27: bench grinder currently considered not required.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>part_ironman_front_dampers_separate_shipment</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5686,22 +5446,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -5712,30 +5472,34 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
+          <t>Bifurcated shipment tracker for the front damper pair arriving separately from the rest of the Ironman kit. Amount is included in the main Ironman kit total to avoid double-counting. Verify 24635FE x2 on receipt before closing suspension procurement.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>part_ironman_foamcell_suspension_kit</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5745,25 +5509,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>575000</v>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5771,30 +5537,34 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
+          <t>User update 2026-05-01: Ironman Foamcell suspension kit ordered from attached parts list; PKR 600000 less PKR 25000 discount = PKR 575000 total. Track as main shipment plus a separate front damper shipment. Supplier list shows part numbers 24635FE, 24636FE, TOY001B, TOY002B, 415UBK, 713UK, 343LH, 343RH, 3523, 346. All previous local spring, OME/Bilstein, separate bushing, shackle, and U-bolt alternatives removed from active parts list.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>part_wiring_kit</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wiring kit</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5804,25 +5574,27 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>2188</v>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5830,30 +5602,34 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00493|akber_khan-00494|akber_khan-00495|user_update_2026-04-22_wiring_built</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Superseded for now because user reports wiring is already built; reopen only if later rewire scope is identified Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>User update: 2 sets purchased and paid; not yet received Gmail Daraz confirmation matched exact item + quantity (2) and total PKR 2188; ETA 2026-04-27..2026-04-29.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5863,25 +5639,27 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>7696</v>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5889,339 +5667,22 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>tool_bench_grinder</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Bench grinder</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>goods</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>not_required</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Toolsmart</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>User update 2026-04-27: bench grinder currently considered not required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>part_ironman_front_dampers_separate_shipment</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>goods</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>pending_delivery</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Ironman 4x4 supplier</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Bifurcated shipment tracker for the front damper pair arriving separately from the rest of the Ironman kit. Amount is included in the main Ironman kit total to avoid double-counting. Verify 24635FE x2 on receipt before closing suspension procurement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>part_old_man_emu_shocks</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>goods</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>pending_delivery</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>575000</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Ironman 4x4 supplier</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>User update 2026-05-01: Ironman Foamcell suspension kit ordered from attached parts list; PKR 600000 less PKR 25000 discount = PKR 575000 total. Track as main shipment plus a separate front damper shipment. Supplier list shows part numbers 24635FE, 24636FE, TOY001B, TOY002B, 415UBK, 713UK, 343LH, 343RH, 3523, 346. All previous local spring, OME/Bilstein, separate bushing, shackle, and U-bolt alternatives removed from active parts list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>goods</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>pending_delivery</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>2188</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Daraz</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>User update: 2 sets purchased and paid; not yet received Gmail Daraz confirmation matched exact item + quantity (2) and total PKR 2188; ETA 2026-04-27..2026-04-29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>part_seam_sealer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Seam sealer</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>goods</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>pending_delivery</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>7696</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Autohub</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
           <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link. Gmail Autohub order 1761310 confirms 3x HB BODY 999 seam sealer and shipment status.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M73"/>
+  <autoFilter ref="A1:M68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6232,7 +5693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6244,9 +5705,9 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -6980,20 +6441,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
+          <t>part_cable_sleeve_protection</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7003,52 +6464,52 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk / HAQ ELECTRIC</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>part_cable_sleeve_protection</t>
+          <t>part_mech_brake_flex_hose_set</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cable sleeve protection</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7058,32 +6519,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / HAQ ELECTRIC</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
@@ -7493,7 +6954,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Electric wires</t>
+          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -7512,7 +6973,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -7527,7 +6988,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>received_candidate</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -8181,7 +7642,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>H4 Ceramic Headlight Connector - H4 - High</t>
+          <t>H4 ceramic headlight connectors - x4 received</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -8190,7 +7651,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8200,22 +7661,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -8225,7 +7686,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
         </is>
       </c>
     </row>
@@ -8397,36 +7858,34 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>quote_hot_rod_wiring</t>
+          <t>part_ironman_front_dampers_separate_shipment</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hot rod wiring quote</t>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>28010</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -8436,29 +7895,29 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>akber_khan-00494|user_update_2026-04-22_wiring_built</t>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_ironman_front_dampers_separate_shipment</t>
+          <t>part_ironman_foamcell_suspension_kit</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8468,11 +7927,13 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>575000</v>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>ordered</t>
@@ -8480,7 +7941,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -8510,149 +7971,149 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_old_man_emu_shocks</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_metal_protection</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" s="5" t="n">
-        <v>575000</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>part_battery_purchase</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" s="5" t="n">
+        <v>20000</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New battery purchase</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>20000</v>
+        <v>2188</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8662,7 +8123,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -8672,48 +8133,46 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>credit_old_battery_return</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>Old battery return credit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>2188</v>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>credited</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8723,127 +8182,117 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>akber_khan-00760</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
+          <t>part_piano_hinge</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>credited</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>akber_khan-00760</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>quote_pet_braided_sleeving</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
+          <t>part_power_steering_upgrade</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PET expandable braided sleeving (100ft 1/4 inch)</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>7414</v>
-      </c>
+          <t>Power steering upgrade</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -8853,42 +8302,42 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>electronicsstore.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
+          <t>part_primer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8898,22 +8347,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -8923,27 +8372,27 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8953,7 +8402,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -8963,12 +8412,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -8978,20 +8427,20 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_primer</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -9033,27 +8482,31 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -9063,111 +8516,113 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" s="5" t="n">
+        <v>7696</v>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>part_self_etching_primer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -9177,106 +8632,100 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>part_sound_dampening_sheets</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>7696</v>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_mech_spark_plugs_set</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Spark plugs set</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -9308,7 +8757,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -9318,27 +8767,27 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -9348,52 +8797,52 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -9403,52 +8852,52 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
+          <t>part_split_conduit_braided_sleeve_small</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Large</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -9458,27 +8907,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -9490,13 +8939,13 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Medium</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -9528,7 +8977,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -9545,13 +8994,13 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve - Small</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -9600,20 +9049,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>tool_tap_set</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Tap set</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -9623,52 +9072,52 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_mech_thermostat_gasket</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Thermostat plus gasket</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -9678,22 +9127,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9703,20 +9152,20 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
+          <t>tool_torque_wrench</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Torque wrench</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -9758,27 +9207,27 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_seed|akber_khan-00395</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
+          <t>part_mech_vacuum_hose_refresh</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Vacuum hose refresh kit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -9788,22 +9237,22 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -9813,27 +9262,27 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
+          <t>part_wax_and_grease_remover</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Wax and grease remover</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9843,68 +9292,62 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>quote_universal_21_circuit_kit</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
+          <t>part_winch_switch</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Universal 21-circuit wiring kit quote</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>43570</v>
-      </c>
+          <t>Winch switch</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -9919,303 +9362,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>akber_khan-00495</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>part_mech_vacuum_hose_refresh</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Vacuum hose refresh kit</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>TBD (confirm)</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>part_wax_and_grease_remover</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Wax and grease remover</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>next_phase_purchase</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Autohub</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>part_winch_switch</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Winch switch</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>TBD (confirm)</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
           <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>quote_wiring_harness</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Wiring harness quote</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="n">
-        <v>34249</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>quote</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>quote_only</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>AliExpress</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>akber_khan-00493</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>part_wiring_kit</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Wiring kit</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>AliExpress</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00493|akber_khan-00494|akber_khan-00495|user_update_2026-04-22_wiring_built</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M70"/>
+  <autoFilter ref="A1:M65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/manual/j40-master-tracker.xlsx
+++ b/data/manual/j40-master-tracker.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase of Services" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Purchase of Services'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-01 01:41:30</t>
+          <t>2026-05-01 03:27:26</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>42737</v>
+        <v>46737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1208,12 +1208,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>part_ironman_foamcell_suspension_kit</t>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>575000</v>
+        <v>54450</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1256,19 +1256,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New battery purchase - installed</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>20000</v>
+        <v>1200</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1301,29 +1301,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2188</v>
+        <v>2380</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1366,19 +1366,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
+          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>7696</v>
+        <v>2050</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1421,28 +1421,28 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
+          <t>part_ironman_foamcell_suspension_kit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>11365</v>
+        <v>575000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1451,92 +1451,532 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>part_battery_purchase</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>New battery purchase - installed</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>registered_purchase</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ghazi Road</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>akber_khan-00753</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2188</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daraz</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Seam sealer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7696</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Wadfow Pressure sprayer WRS1550</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>admin_excise_challan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Excise challan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>11365</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>registered_purchase</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fj40 group</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fj40-00025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>admin_vehicle_inspection</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Vehicle inspection</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>services</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D22" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>registered_purchase</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Fj40 group</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>needs_confirmation</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>fj40-00025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1547,7 +1987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2080,17 +2520,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
+          <t>part_rubber_grommet_set</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2105,22 +2545,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>received</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>-4000</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2128,34 +2566,30 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>akber_khan-00760</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PKR 4,000 return value received against the old battery; net new-battery cost is PKR 16,000.</t>
+          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html. User correction 2026-05-01: current tracker image is incorrect; require exact order/received photo before treating image as evidence.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>part_split_conduit_braided_sleeve_medium</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2191,30 +2625,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html</t>
+          <t>Covered by received workbook sleeve inventory (14mm and 16mm, 5m lengths). No additional medium sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2260,20 +2694,20 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (14mm and 16mm, 5m lengths). No additional medium sleeve required until physical count shows a gap.</t>
+          <t>Covered by received workbook sleeve inventory (20mm, 5m lengths). No additional large sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
+          <t>part_split_conduit_braided_sleeve_small</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2319,25 +2753,29 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (20mm, 5m lengths). No additional large sleeve required until physical count shows a gap.</t>
+          <t>Covered by received workbook sleeve inventory (8mm and 10mm, 5m lengths). No additional small sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>admin_excise_challan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
+          <t>Excise challan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2352,15 +2790,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>received</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>11365</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2368,24 +2808,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (8mm and 10mm, 5m lengths). No additional small sleeve required until physical count shows a gap.</t>
+          <t>Vehicle transfer cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
+          <t>admin_vehicle_purchase</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2395,7 +2835,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>Vehicle purchase price</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2423,9 +2863,7 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>11365</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2433,59 +2871,55 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>fj40-00014</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Vehicle transfer cost mentioned in the group chat</t>
+          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>admin_vehicle_purchase</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>part_mech_air_filter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vehicle purchase price</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2496,30 +2930,30 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>fj40-00014</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
+          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
+          <t>tool_cover</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2555,30 +2989,30 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
+          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tool_cover</t>
+          <t>part_copper_grease</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2614,30 +3048,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>user_seed</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>part_evaporust_5l</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2673,34 +3111,30 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>part_evaporust_5l</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>tool_grease_gun</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2736,30 +3170,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7mart</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
+          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
+          <t>part_hidden_diesel_cutoff_switch</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Hidden diesel cutoff switch (binary toggle)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2795,30 +3229,34 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
+          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>part_hidden_diesel_cutoff_switch</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>credit_old_battery_return</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hidden diesel cutoff switch (binary toggle)</t>
+          <t>Old battery return credit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2838,12 +3276,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,17 +3292,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
+          <t>akber_khan-00760|user_update_2026-05-01_battery_credit_wrong</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
+          <t>User correction 2026-05-01: previous PKR 4,000 old-battery return credit is wrong. Removed from confirmed totals until corrected amount/source is provided.</t>
         </is>
       </c>
     </row>
@@ -4004,13 +4442,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>tool_electrical_test_kit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4035,10 +4477,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>8811</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -4046,34 +4490,30 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore if distributor ignition remains</t>
+          <t>User update 2026-04-27: no reliable order evidence for ANENG ST170 test kit; keep as unconfirmed/not ordered until explicit proof is found.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
+          <t>part_mech_engine_mount_set</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Engine mount set</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4101,9 +4541,7 @@
           <t>next_phase_purchase</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>8811</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -4111,30 +4549,30 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>User update 2026-04-27: no reliable order evidence for ANENG ST170 test kit; keep as unconfirmed/not ordered until explicit proof is found.</t>
+          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_mech_engine_mount_set</t>
+          <t>part_mech_engine_oil_filter_service</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Engine mount set</t>
+          <t>Engine oil + oil filter service pack</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4159,7 +4597,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4180,20 +4618,20 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_mech_engine_oil_filter_service</t>
+          <t>part_epoxy_primer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Engine oil + oil filter service pack</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4218,7 +4656,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4234,25 +4672,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
+          <t>part_foam</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4277,7 +4715,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4298,20 +4736,20 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_foam</t>
+          <t>part_mech_fuel_filter</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4336,7 +4774,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4352,25 +4790,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
+          <t>part_mech_fuel_hose_and_clamps</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4411,25 +4849,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Spec: diesel-rated SAE J30R9/J30R14T2 or DIN 73379-3E hose; 8 mm feed, 6 mm return/bleed, 3.2-3.5 mm injector leak-off only after measuring actual nipples. Use fuel-injection clamps. Do not fabricate high-pressure injector pipes.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
+          <t>part_mech_heater_hose_set</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4470,25 +4908,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE old soft fuel lines during full restore</t>
+          <t>Spec: front heater hoses Toyota 99552-30500 L=400 and 99552-30300 L=280 or EPDM SAE J20R3 heater hose matched to heater/engine nipples, expected 16 mm / 5/8 inch ID after measurement. Include clamps and confirm whether rear heater circuit exists.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
+          <t>part_horn_relay</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4529,25 +4967,25 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
+          <t>part_metal_protection</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4583,30 +5021,30 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
+          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
+          <t>part_primer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4642,30 +5080,30 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
+          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_primer</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4706,25 +5144,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
+          <t>Spec: Toyota radiator cap 16401-41021 or exact pressure-equivalent cap for the fitted radiator neck; replace with coolant hose service.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4765,25 +5203,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Spec: 2H/HJ47 molded EPDM coolant hoses, upper Toyota 16571-68020 and lower Toyota 16572-68020; clamp refs 90460-50016/96111-10500 plus lower outlet 96111-10560. Verify actual radiator and thermostat housing geometry before payment.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
+          <t>part_self_etching_primer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4808,7 +5246,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -4824,25 +5262,25 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4867,7 +5305,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -4883,25 +5321,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4926,7 +5364,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -4942,25 +5380,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5001,25 +5439,25 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>part_mech_vacuum_hose_refresh</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Vacuum hose refresh kit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5044,7 +5482,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -5060,25 +5498,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
+          <t>Spec: reinforced vacuum hose matched to actual barbs; brake booster/vacuum pump hose must not collapse. 2H vacuum-pump oil outlet hose OEM 90923-02079 if that hose is fitted. Replace suspect check valves and clips.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_wax_and_grease_remover</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Wax and grease remover</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5103,7 +5541,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -5114,30 +5552,30 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
+          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_winch_switch</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Winch switch</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5162,7 +5600,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -5178,25 +5616,25 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE old brittle vacuum lines during full restore</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>part_power_steering_upgrade</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5206,7 +5644,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5216,12 +5654,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -5232,30 +5670,30 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
+          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
+          <t>tool_bench_grinder</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>Bench grinder</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5265,7 +5703,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5275,7 +5713,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5291,30 +5729,30 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
+          <t>User update 2026-04-27: bench grinder currently considered not required.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5324,7 +5762,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5334,12 +5772,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -5355,25 +5793,29 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
+          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; no distributor ignition tune-up item required.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tool_bench_grinder</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bench grinder</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5388,20 +5830,22 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>54450</v>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5409,24 +5853,24 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>User update 2026-04-27: bench grinder currently considered not required.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; primary 3T trolley jack for lifting before supporting chassis on stands.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>part_ironman_front_dampers_separate_shipment</t>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5436,7 +5880,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5451,7 +5895,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5464,7 +5908,9 @@
           <t>ordered_pending_delivery</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" s="5" t="n">
+        <v>1200</v>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5472,24 +5918,24 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Bifurcated shipment tracker for the front damper pair arriving separately from the rest of the Ironman kit. Amount is included in the main Ironman kit total to avoid double-counting. Verify 24635FE x2 on receipt before closing suspension procurement.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; clamp set for holding pads, small parts, and temporary setup during cleaning/bodywork.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>part_ironman_foamcell_suspension_kit</t>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5499,7 +5945,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5514,7 +5960,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5528,7 +5974,7 @@
         </is>
       </c>
       <c r="I66" s="5" t="n">
-        <v>575000</v>
+        <v>2380</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -5537,34 +5983,30 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>User update 2026-05-01: Ironman Foamcell suspension kit ordered from attached parts list; PKR 600000 less PKR 25000 discount = PKR 575000 total. Track as main shipment plus a separate front damper shipment. Supplier list shows part numbers 24635FE, 24636FE, TOY001B, TOY002B, 415UBK, 713UK, 343LH, 343RH, 3523, 346. All previous local spring, OME/Bilstein, separate bushing, shackle, and U-bolt alternatives removed from active parts list.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; soft mallet for non-marring persuasion and aluminium/bodywork shaping.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
+          <t>part_mech_heat_glow_plugs_set</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>Heat/glow plugs set - diesel 2H</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5579,22 +6021,20 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>2188</v>
-      </c>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5602,87 +6042,664 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>User update: 2 sets purchased and paid; not yet received Gmail Daraz confirmation matched exact item + quantity (2) and total PKR 2188; ETA 2026-04-27..2026-04-29.</t>
+          <t>Diesel baseline item. Buy NEW only; confirm fitted engine code plus current plug voltage/thread/reach or old plug part number before payment.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>2050</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; dead blow mallet for controlled non-rebound strikes during suspension/bodywork setup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>part_ironman_front_dampers_separate_shipment</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Ironman 4x4 supplier</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Bifurcated shipment tracker for the front damper pair arriving separately from the rest of the Ironman kit. Amount is included in the main Ironman kit total to avoid double-counting. Verify 24635FE x2 on receipt before closing suspension procurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>part_ironman_foamcell_suspension_kit</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>575000</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ironman 4x4 supplier</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>User update 2026-05-01: Ironman Foamcell suspension kit ordered from attached parts list; PKR 600000 less PKR 25000 discount = PKR 575000 total. Track as main shipment plus a separate front damper shipment. Supplier list shows part numbers 24635FE, 24636FE, TOY001B, TOY002B, 415UBK, 713UK, 343LH, 343RH, 3523, 346. All previous local spring, OME/Bilstein, separate bushing, shackle, and U-bolt alternatives removed from active parts list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>2188</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Daraz</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>User update: 2 sets purchased and paid; not yet received Gmail Daraz confirmation matched exact item + quantity (2) and total PKR 2188; ETA 2026-04-27..2026-04-29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>part_seam_sealer</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Seam sealer</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>goods</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>pending_delivery</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>ordered_pending_delivery</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n">
+      <c r="I72" s="5" t="n">
         <v>7696</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Autohub</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link. Gmail Autohub order 1761310 confirms 3x HB BODY 999 seam sealer and shipment status.</t>
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>part_mech_spark_plugs_set</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Spark plugs set</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>not_required_diesel_engine</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; replaced in active baseline by diesel heat/glow plugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; quantity 2 pairs at PKR 9600 each, four stands total for chassis support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; one of 9 physical items in PKR 94510 order for chassis lift/clean/suspension work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; hammer and dolly set for aluminium/body panel shaping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wadfow Pressure sprayer WRS1550</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; 5L sprayer for water-based degreaser application during chassis/engine/transmission cleaning.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M68"/>
+  <autoFilter ref="A1:M77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5693,7 +6710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5701,11 +6718,11 @@
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
@@ -6902,7 +7919,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6912,7 +7929,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -6922,12 +7939,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6937,7 +7954,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
@@ -7509,7 +8526,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
     </row>
@@ -7693,189 +8710,203 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" s="5" t="n">
+        <v>54450</v>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>part_hidden_diesel_cutoff_switch</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hidden diesel cutoff switch (binary toggle)</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" s="5" t="n">
+        <v>1200</v>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" s="5" t="n">
+        <v>2380</v>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>part_ironman_front_dampers_separate_shipment</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_heat_glow_plugs_set</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+          <t>Heat/glow plugs set - diesel 2H</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>new_only_planned</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7890,108 +8921,102 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_ironman_foamcell_suspension_kit</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_heater_hose_set</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" s="5" t="n">
-        <v>575000</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
+          <t>part_hidden_diesel_cutoff_switch</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Hidden diesel cutoff switch (binary toggle)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8001,115 +9026,109 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
+          <t>part_horn_relay</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New battery purchase - installed</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>2188</v>
+        <v>2050</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -8143,101 +9162,107 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
+          <t>part_ironman_front_dampers_separate_shipment</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>credited</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>akber_khan-00760</t>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>part_ironman_foamcell_suspension_kit</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>575000</v>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -8247,42 +9272,42 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
+          <t>part_metal_protection</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8292,7 +9317,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -8302,204 +9327,216 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_primer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>part_battery_purchase</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" s="5" t="n">
+        <v>20000</v>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" s="5" t="n">
+        <v>2188</v>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>credit_old_battery_return</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Old battery return credit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>disputed</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>akber_khan-00760|user_update_2026-05-01_battery_credit_wrong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>part_piano_hinge</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -8516,12 +9553,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8536,86 +9573,80 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>part_power_steering_upgrade</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>7696</v>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_primer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -8647,7 +9678,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -8657,20 +9688,20 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -8702,7 +9733,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -8712,20 +9743,20 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -8767,20 +9798,24 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -8817,87 +9852,93 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" s="5" t="n">
+        <v>7696</v>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_self_etching_primer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8907,45 +9948,45 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -8977,7 +10018,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -8987,27 +10028,27 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_mech_spark_plugs_set</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Spark plugs set</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -9017,7 +10058,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -9027,12 +10068,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -9042,20 +10083,20 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -9072,12 +10113,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -9092,25 +10133,25 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -9127,12 +10168,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -9147,25 +10188,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
+          <t>part_split_conduit_braided_sleeve_small</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -9182,12 +10223,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -9202,25 +10243,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -9252,7 +10293,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -9262,20 +10303,20 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -9307,77 +10348,596 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
+          <t>tool_tap_set</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>Tap set</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ToolsMart.pk</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>part_mech_thermostat_gasket</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Thermostat plus gasket</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>tool_torque_wrench</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Torque wrench</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>ToolsMart.pk</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00395</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>part_mech_vacuum_hose_refresh</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Vacuum hose refresh kit</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>not_paid</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>not_ordered</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Wadfow Pressure sprayer WRS1550</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>part_wax_and_grease_remover</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wax and grease remover</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>part_winch_switch</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Winch switch</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>deferred_optional</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>TBD (confirm)</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M65"/>
+  <autoFilter ref="A1:M74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/manual/j40-master-tracker.xlsx
+++ b/data/manual/j40-master-tracker.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase of Services" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Purchase of Services'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-01 03:27:26</t>
+          <t>2026-05-02 06:35:27</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>46737</v>
+        <v>48925</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -747,16 +747,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -823,12 +823,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>part_autohub_diss_apc_cleaner_5l</t>
+          <t>tool_daraz_mini_wire_brush_set_x2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DISS (APC) All Purpose Cleaner 5L</t>
+          <t>3 pc mini wire brush set - brass, nylon, stainless steel bristles x2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>4999</v>
+        <v>561</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Daraz / Bunyad Collection (Karachi)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -861,29 +861,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>gmail_msg_19de62bcd140fa41|gmail_order_242365766980938</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>part_dielectric_grease</t>
+          <t>tool_daraz_75mm_knotted_cup_wire_brush_x2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dielectric grease</t>
+          <t>75mm 3 inch steel knotted cup rotary wire brush for angle grinder x2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>5609</v>
+        <v>3896</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Adenwalla &amp; Sons</t>
+          <t>Daraz / Al Rehman Mart (Lahore)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -916,29 +916,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
+          <t>gmail_msg_19de62bcd3dd7207|gmail_order_242365766280938</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>part_electric_wires</t>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>11529</v>
+        <v>4999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -981,19 +981,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
+          <t>part_dielectric_grease</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>8811</v>
+        <v>5609</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1011,44 +1011,44 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
+          <t>part_electric_wires</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
+          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7860</v>
+        <v>11529</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1066,44 +1066,44 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>quoted_initial</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
+          <t>tool_electrical_test_kit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3250</v>
+        <v>8811</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1121,44 +1121,44 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>part_h4_ceramic_headlight_connector_high</t>
+          <t>quote_rubber_grommet_set_chat</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H4 ceramic headlight connectors - x4 received</t>
+          <t>Electrical wire grommet set (200pcs)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1350</v>
+        <v>7860</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1176,44 +1176,44 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>quoted_initial</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Auto Xpert Pakistan</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
+          <t>fj40-00276</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tool_harden_3ton_trolley_jack_730213</t>
+          <t>tool_autohub_engine_detailing_brush_bundle_62191</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
+          <t>Engine/detailing brush bundle - tire sidewall brush, large detailing brush, 5 pc detailing brush set</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>54450</v>
+        <v>2588</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1256,19 +1256,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>gmail_msg_19de62cf4907c036|gmail_order_1762191|autohub_order_62191</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tool_harden_spring_clamp_set_4in_6pc</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1200</v>
+        <v>3250</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1301,29 +1301,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tool_harden_white_rubber_mallet_700g_590437</t>
+          <t>part_h4_ceramic_headlight_connector_high</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
+          <t>H4 ceramic headlight connectors - x4 received</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2380</v>
+        <v>1350</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2050</v>
+        <v>54450</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1421,19 +1421,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_ironman_foamcell_suspension_kit</t>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>575000</v>
+        <v>1200</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New battery purchase - installed</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>20000</v>
+        <v>2380</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1521,29 +1521,29 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>tool_powerhouse_ingco_wb30501_wire_cup_brush_x3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>INGCO WB30501 Wire Cup Brush x3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2188</v>
+        <v>1065</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Powerhouse Express</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1586,19 +1586,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>gmail_msg_19de632df983464c|gmail_order_26242</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
+          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>7696</v>
+        <v>2050</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1641,19 +1641,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+          <t>part_ironman_foamcell_suspension_kit</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>19200</v>
+        <v>575000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1696,19 +1696,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+          <t>part_daraz_jubilee_hose_clip_assortment_30pc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Total Wrecking bar 600mm THT431242</t>
+          <t>Jubilee hose clip assortment - 10 pc fuel line/diesel/petrol/coolant clamp packs x3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>2860</v>
+        <v>2390</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Daraz / Gravax corporation</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1751,19 +1751,19 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>gmail_msg_19de62bcdb1080ff|gmail_order_242365766580938</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+          <t>part_battery_purchase</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>9870</v>
+        <v>20000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1796,29 +1796,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wadfow Pressure sprayer WRS1550</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2500</v>
+        <v>2188</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>registered_purchase</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1851,38 +1851,38 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg|gmail_msg_19dd86b5fbb89675|gmail_delivery_241938794080938</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
+          <t>tool_daraz_safety_goggles_cleanup</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>Safety goggles / protective glasses for grinding and cleaning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>11365</v>
+        <v>764</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>registered_purchase</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>Daraz / Reliable_Shop</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1906,77 +1906,407 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>gmail_msg_19de62bcddc3ff3a|gmail_order_242365766080938</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Seam sealer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>7696</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Wadfow Pressure sprayer WRS1550</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>admin_excise_challan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Excise challan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>11365</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>registered_purchase</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fj40 group</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fj40-00025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>admin_vehicle_inspection</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Vehicle inspection</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>services</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>registered_purchase</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Fj40 group</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>needs_confirmation</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>fj40-00025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K22"/>
+  <autoFilter ref="A1:K28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1987,10 +2317,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2187,7 +2517,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2378,7 +2708,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2513,24 +2843,24 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>New battery is already purchased and installed. Gross PKR 20,000 before old-battery return credit.</t>
+          <t>New battery is already purchased and installed. Gross PKR 20,000 retained.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2558,7 +2888,9 @@
           <t>received</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" s="5" t="n">
+        <v>2188</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2566,30 +2898,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg|gmail_msg_19dd86b5fbb89675|gmail_delivery_241938794080938</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html. User correction 2026-05-01: current tracker image is incorrect; require exact order/received photo before treating image as evidence.</t>
+          <t>Daraz order 241938794080938 was delivered per Gmail delivery confirmation dated 2026-04-29. Original order matched exact item + quantity (2) and total PKR 2188.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2625,30 +2961,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (14mm and 16mm, 5m lengths). No additional medium sleeve required until physical count shows a gap.</t>
+          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html. User correction 2026-05-01: current tracker image is incorrect; require exact order/received photo before treating image as evidence.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2694,20 +3030,20 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (20mm, 5m lengths). No additional large sleeve required until physical count shows a gap.</t>
+          <t>Covered by received workbook sleeve inventory (14mm and 16mm, 5m lengths). No additional medium sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2753,29 +3089,25 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (8mm and 10mm, 5m lengths). No additional small sleeve required until physical count shows a gap.</t>
+          <t>Covered by received workbook sleeve inventory (20mm, 5m lengths). No additional large sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>part_split_conduit_braided_sleeve_small</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2790,17 +3122,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>11365</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2808,24 +3138,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Vehicle transfer cost mentioned in the group chat</t>
+          <t>Covered by received workbook sleeve inventory (8mm and 10mm, 5m lengths). No additional small sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>admin_vehicle_purchase</t>
+          <t>admin_excise_challan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2835,7 +3165,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vehicle purchase price</t>
+          <t>Excise challan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2863,7 +3193,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" s="5" t="n">
+        <v>11365</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2871,55 +3203,59 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>fj40-00014</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
+          <t>Vehicle transfer cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>admin_vehicle_purchase</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Vehicle purchase price</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2930,30 +3266,30 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>fj40-00014</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
+          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tool_cover</t>
+          <t>part_mech_air_filter</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2989,30 +3325,30 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
+          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
+          <t>tool_cover</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,34 +3384,30 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>part_evaporust_5l</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>part_copper_grease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3111,30 +3443,34 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7mart</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
+          <t>user_seed</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>part_evaporust_5l</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3170,30 +3506,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
+          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>part_hidden_diesel_cutoff_switch</t>
+          <t>tool_grease_gun</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hidden diesel cutoff switch (binary toggle)</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3229,34 +3565,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
+          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
+          <t>part_hidden_diesel_cutoff_switch</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>Hidden diesel cutoff switch (binary toggle)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3276,12 +3608,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3292,17 +3624,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>akber_khan-00760|user_update_2026-05-01_battery_credit_wrong</t>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>User correction 2026-05-01: previous PKR 4,000 old-battery return credit is wrong. Removed from confirmed totals until corrected amount/source is provided.</t>
+          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
         </is>
       </c>
     </row>
@@ -4088,13 +4420,13 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>part_body_mount_hardware_kit</t>
+          <t>part_carpet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Body mount hardware kit bolts sleeves washers</t>
+          <t>Carpet</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4119,7 +4451,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4135,25 +4467,25 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>New graded hardware required for reliable tub refit</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>part_body_mount_shim_pack</t>
+          <t>part_mech_clutch_master_slave_refresh</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Body mount shim and spacer pack</t>
+          <t>Clutch master and slave cylinder refresh kit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4178,7 +4510,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4194,25 +4526,29 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Shim set needed for mount alignment during trial fit</t>
+          <t>MECH INSPECT THEN REPLACE if leakage pedal sink or seized seals</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>part_body_mount_rubber_kit</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>tool_electrical_test_kit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Body-to-chassis mount rubber kit</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4237,10 +4573,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>8811</v>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -4248,30 +4586,30 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Replace all tub mounts before final body refit torque</t>
+          <t>User update 2026-04-27: no reliable order evidence for ANENG ST170 test kit; keep as unconfirmed/not ordered until explicit proof is found.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
+          <t>part_mech_engine_mount_set</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Engine mount set</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4296,7 +4634,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4317,20 +4655,20 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>MECH SAFETY MUST REPLACE during full restore before final road validation</t>
+          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>part_carpet</t>
+          <t>part_mech_engine_oil_filter_service</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Carpet</t>
+          <t>Engine oil + oil filter service pack</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4355,7 +4693,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4371,25 +4709,25 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_mech_clutch_master_slave_refresh</t>
+          <t>part_epoxy_primer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Clutch master and slave cylinder refresh kit</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4430,29 +4768,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>MECH INSPECT THEN REPLACE if leakage pedal sink or seized seals</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
+          <t>part_foam</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4477,12 +4811,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>8811</v>
-      </c>
+          <t>deferred_until_body_closed</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -4490,30 +4822,30 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>User update 2026-04-27: no reliable order evidence for ANENG ST170 test kit; keep as unconfirmed/not ordered until explicit proof is found.</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_mech_engine_mount_set</t>
+          <t>part_mech_fuel_filter</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Engine mount set</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4538,7 +4870,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4559,20 +4891,20 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>MECH INSPECT THEN REPLACE if cracked sagging or oil-soaked</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_mech_engine_oil_filter_service</t>
+          <t>part_horn_relay</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Engine oil + oil filter service pack</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4613,25 +4945,25 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
+          <t>part_metal_protection</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4656,7 +4988,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4667,30 +4999,30 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_foam</t>
+          <t>part_primer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4715,7 +5047,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4731,25 +5063,25 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4790,25 +5122,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Spec: Toyota radiator cap 16401-41021 or exact pressure-equivalent cap for the fitted radiator neck; replace with coolant hose service.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
+          <t>part_rear_axle_hard_brake_lines</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Rear axle hard brake lines and fittings</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4833,7 +5165,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -4849,25 +5181,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>BR-REAR-002|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Spec: diesel-rated SAE J30R9/J30R14T2 or DIN 73379-3E hose; 8 mm feed, 6 mm return/bleed, 3.2-3.5 mm injector leak-off only after measuring actual nipples. Use fuel-injection clamps. Do not fabricate high-pressure injector pipes.</t>
+          <t>Recreate left/right rear axle lines in brake-rated 3/16 in / 4.75 mm tube after flare standard, fitting threads, bend templates, and clip positions are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
+          <t>part_rear_brake_line_cable_clips</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Rear brake line clips and parking-brake cable retainers</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4892,7 +5224,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -4908,25 +5240,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>BR-REAR-006|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Spec: front heater hoses Toyota 99552-30500 L=400 and 99552-30300 L=280 or EPDM SAE J20R3 heater hose matched to heater/engine nipples, expected 16 mm / 5/8 inch ID after measurement. Include clamps and confirm whether rear heater circuit exists.</t>
+          <t>Count and replace corroded or missing brake-line clips, cable retainers, rubber sleeves, grommets, and rubber-lined P-clips before final rear axle routing.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
+          <t>part_rear_brake_shoes_hardware</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Rear brake shoes and spring hardware set</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4951,7 +5283,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>inspect_then_buy</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -4967,25 +5299,25 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>BR-REAR-005|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
+          <t>Order shoes, return springs, hold-down springs, adjusters, and retainers after drum diameter, shoe width, and backing-plate family are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
+          <t>part_rear_center_brake_flex_hose</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Rear center frame-to-axle flexible brake hose</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5010,7 +5342,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5021,30 +5353,30 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>BR-REAR-003|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
+          <t>Replace rear center hose once chassis-side and axle-side fitting threads/end styles and full-droop slack are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_primer</t>
+          <t>part_rear_parking_brake_cable_set</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Rear parking brake cable set with clips and equalizer hardware</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5069,7 +5401,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5085,25 +5417,25 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>BR-REAR-001|20260501_194305_gp_EllBGvXA|20260501_194322_gp_XuRtjN4w</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
+          <t>Replace the rear handbrake/parking-brake cable system as a safety baseline; order only after cable end types, lengths, equalizer hardware, and backing-plate levers are confirmed from the removed samples.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
+          <t>part_rear_wheel_cylinders_pair</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Rear wheel cylinders pair with bleed screws</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5128,7 +5460,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>inspect_then_buy</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5144,25 +5476,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>BR-REAR-004|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Spec: Toyota radiator cap 16401-41021 or exact pressure-equivalent cap for the fitted radiator neck; replace with coolant hose service.</t>
+          <t>Buy as a left/right pair after drum opening confirms cylinder bore, port thread, mounting pattern, and pushrod style.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
+          <t>part_self_etching_primer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5187,7 +5519,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5203,25 +5535,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Spec: 2H/HJ47 molded EPDM coolant hoses, upper Toyota 16571-68020 and lower Toyota 16572-68020; clamp refs 90460-50016/96111-10500 plus lower outlet 96111-10560. Verify actual radiator and thermostat housing geometry before payment.</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5246,7 +5578,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5262,25 +5594,25 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5305,7 +5637,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5321,25 +5653,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5364,7 +5696,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5385,20 +5717,20 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_wax_and_grease_remover</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Wax and grease remover</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5423,7 +5755,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -5434,30 +5766,30 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
+          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_winch_switch</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Winch switch</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5482,7 +5814,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -5498,25 +5830,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Spec: reinforced vacuum hose matched to actual barbs; brake booster/vacuum pump hose must not collapse. 2H vacuum-pump oil outlet hose OEM 90923-02079 if that hose is fitted. Replace suspect check valves and clips.</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>part_power_steering_upgrade</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5526,7 +5858,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5536,12 +5868,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -5552,30 +5884,34 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
+          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>tool_daraz_mini_wire_brush_set_x2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>3 pc mini wire brush set - brass, nylon, stainless steel bristles x2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5585,25 +5921,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>561</v>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5611,30 +5949,34 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Bunyad Collection (Karachi)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>gmail_msg_19de62bcd140fa41|gmail_order_242365766980938</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
+          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Two 3 pc mini wire brush sets at PKR 198 each; subtotal PKR 396 plus PKR 165 shipping. Product link: https://www.daraz.pk/products/i192752152-s1385484991.html?urlFlag=true&amp;mp=1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>tool_daraz_75mm_knotted_cup_wire_brush_x2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>75mm 3 inch steel knotted cup rotary wire brush for angle grinder x2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5644,25 +5986,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>researching</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>3896</v>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5670,17 +6014,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Al Rehman Mart (Lahore)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>gmail_msg_19de62bcd3dd7207|gmail_order_242365766280938</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
+          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Quantity 2 at PKR 1878 each; subtotal PKR 3756 plus PKR 140 shipping. Product link: https://www.daraz.pk/products/i2171955-s1269424717.html?urlFlag=true&amp;mp=1</t>
         </is>
       </c>
     </row>
@@ -5746,13 +6090,13 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
+          <t>part_body_mount_hardware_kit</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>Body mount hardware kit bolts sleeves washers</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5772,12 +6116,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -5793,29 +6137,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; no distributor ignition tune-up item required.</t>
+          <t>Spec ready: sleeves 8 blanks; cups 14; M10 trial bolts 16; nuts washers and repair pack defined. Complete BMA-006/BMA-007 before final sleeve cutting and bolt length selection.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tool_harden_3ton_trolley_jack_730213</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_body_mount_shim_pack</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
+          <t>Body mount shim and spacer pack</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5830,22 +6170,20 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>54450</v>
-      </c>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5853,34 +6191,30 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; primary 3T trolley jack for lifting before supporting chassis on stands.</t>
+          <t>Spec ready: thin shim pack 1/2/3/5 mm x12 each plus thick control pack 5/10/15 mm x4 each. Complete BMA-008 station measurement before final use.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tool_harden_spring_clamp_set_4in_6pc</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_body_mount_rubber_kit</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
+          <t>Body-to-chassis mount rubber kit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5895,22 +6229,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>1200</v>
-      </c>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5918,34 +6250,30 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; clamp set for holding pads, small parts, and temporary setup during cleaning/bodywork.</t>
+          <t>Spec ready with quantities in body_mount_order_release_specs.csv; complete BMA-001/BMA-002 route decision before committing purchase.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tool_harden_white_rubber_mallet_700g_590437</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_brake_flex_hose_set</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5960,22 +6288,20 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>2380</v>
-      </c>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5983,30 +6309,30 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_plan_2026-04-12_engine_bay_review|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; soft mallet for non-marring persuasion and aluminium/bodywork shaping.</t>
+          <t>Spec ready: order line RPO-BRAKE-001A defines brake-fluid-rated flex hoses matched to current front/rear fittings and full-droop length. Complete RPA-006 fitting photos and full-droop slack check before payment.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>part_mech_heat_glow_plugs_set</t>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Heat/glow plugs set - diesel 2H</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6026,12 +6352,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -6052,24 +6378,24 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Diesel baseline item. Buy NEW only; confirm fitted engine code plus current plug voltage/thread/reach or old plug part number before payment.</t>
+          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; no distributor ignition tune-up item required.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
+          <t>tool_autohub_engine_detailing_brush_bundle_62191</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
+          <t>Engine/detailing brush bundle - tire sidewall brush, large detailing brush, 5 pc detailing brush set</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6098,7 +6424,7 @@
         </is>
       </c>
       <c r="I68" s="5" t="n">
-        <v>2050</v>
+        <v>2588</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -6107,34 +6433,30 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>gmail_msg_19de62cf4907c036|gmail_order_1762191|autohub_order_62191</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; dead blow mallet for controlled non-rebound strikes during suspension/bodywork setup.</t>
+          <t>Autohub order 1762191 / order number 62191 confirmed 2026-05-02: Tire Side Wall Cleaning Brush x1, Detailing Brush Large x1, 5 Pcs Detailing Brush Set x1; subtotal PKR 2339 plus PKR 249 shipping. Links: https://autohub.pk/products/tire-side-wall-cleaning-brush ; https://autohub.pk/products/detailing-brush-large-16-no ; https://autohub.pk/products/5-pcs-detailing-brush-set</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>part_ironman_front_dampers_separate_shipment</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_fuel_hose_and_clamps</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6149,17 +6471,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -6170,24 +6492,24 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Bifurcated shipment tracker for the front damper pair arriving separately from the rest of the Ironman kit. Amount is included in the main Ironman kit total to avoid double-counting. Verify 24635FE x2 on receipt before closing suspension procurement.</t>
+          <t>Spec ready: order lines RPO-FUEL-001A through RPO-FUEL-001C define diesel-rated SAE J30R9/J30R14T2 or DIN 73379-3E hose; 8 mm feed x3 m, 6 mm return x2 m, 3.2-3.5 mm leak-off x1 m. Complete RPA-002/RPA-004 before payment. Do not fabricate high-pressure injector pipes.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>part_ironman_foamcell_suspension_kit</t>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6197,7 +6519,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6212,7 +6534,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6226,7 +6548,7 @@
         </is>
       </c>
       <c r="I70" s="5" t="n">
-        <v>575000</v>
+        <v>54450</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6235,34 +6557,34 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>User update 2026-05-01: Ironman Foamcell suspension kit ordered from attached parts list; PKR 600000 less PKR 25000 discount = PKR 575000 total. Track as main shipment plus a separate front damper shipment. Supplier list shows part numbers 24635FE, 24636FE, TOY001B, TOY002B, 415UBK, 713UK, 343LH, 343RH, 3523, 346. All previous local spring, OME/Bilstein, separate bushing, shackle, and U-bolt alternatives removed from active parts list.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; primary 3T trolley jack for lifting before supporting chassis on stands. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6291,7 +6613,7 @@
         </is>
       </c>
       <c r="I71" s="5" t="n">
-        <v>2188</v>
+        <v>1200</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6300,34 +6622,34 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>User update: 2 sets purchased and paid; not yet received Gmail Daraz confirmation matched exact item + quantity (2) and total PKR 2188; ETA 2026-04-27..2026-04-29.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; clamp set for holding pads, small parts, and temporary setup during cleaning/bodywork. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6342,7 +6664,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6356,7 +6678,7 @@
         </is>
       </c>
       <c r="I72" s="5" t="n">
-        <v>7696</v>
+        <v>2380</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -6365,30 +6687,30 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link. Gmail Autohub order 1761310 confirms 3x HB BODY 999 seam sealer and shipment status.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; soft mallet for non-marring persuasion and aluminium/bodywork shaping. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_mech_heat_glow_plugs_set</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Heat/glow plugs set - diesel 2H</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6408,12 +6730,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -6434,24 +6756,20 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; replaced in active baseline by diesel heat/glow plugs.</t>
+          <t>Diesel baseline item. Buy NEW only; confirm fitted engine code plus current plug voltage/thread/reach or old plug part number before payment.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_heater_hose_set</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6466,22 +6784,20 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>19200</v>
-      </c>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -6489,34 +6805,34 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; quantity 2 pairs at PKR 9600 each, four stands total for chassis support.</t>
+          <t>Spec ready: order lines RPO-COOL-004A and RPO-COOL-004B define Toyota 99552-30500 L=400 and 99552-30300 L=280 or EPDM SAE J20R3 local hose, expected 16 mm / 5/8 inch ID. Complete RPA-002 nipple measurements and rear-heater check before payment.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+          <t>tool_powerhouse_ingco_wb30501_wire_cup_brush_x3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Total Wrecking bar 600mm THT431242</t>
+          <t>INGCO WB30501 Wire Cup Brush x3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6545,7 +6861,7 @@
         </is>
       </c>
       <c r="I75" s="5" t="n">
-        <v>2860</v>
+        <v>1065</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -6554,24 +6870,24 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Powerhouse Express</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>gmail_msg_19de632df983464c|gmail_order_26242</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; one of 9 physical items in PKR 94510 order for chassis lift/clean/suspension work.</t>
+          <t>Order #26242 confirmed 2026-05-02 for 3x INGCO WB30501 wire cup brushes; subtotal PKR 765 plus PKR 300 shipping. Product link: https://powerhouseexpress.com.pk/products/ingco-wb30501-wire-cup-brush</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6581,7 +6897,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6610,7 +6926,7 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>9870</v>
+        <v>2050</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -6624,82 +6940,777 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; hammer and dolly set for aluminium/body panel shaping.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; dead blow mallet for controlled non-rebound strikes during suspension/bodywork setup. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>part_ironman_front_dampers_separate_shipment</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Ironman 4x4 supplier</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Bifurcated shipment tracker for the front damper pair arriving separately from the rest of the Ironman kit. Amount is included in the main Ironman kit total to avoid double-counting. Verify 24635FE x2 on receipt before closing suspension procurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>part_ironman_foamcell_suspension_kit</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>575000</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Ironman 4x4 supplier</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>User update 2026-05-01: Ironman Foamcell suspension kit ordered from attached parts list; PKR 600000 less PKR 25000 discount = PKR 575000 total. Track as main shipment plus a separate front damper shipment. Supplier list shows part numbers 24635FE, 24636FE, TOY001B, TOY002B, 415UBK, 713UK, 343LH, 343RH, 3523, 346. All previous local spring, OME/Bilstein, separate bushing, shackle, and U-bolt alternatives removed from active parts list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>part_daraz_jubilee_hose_clip_assortment_30pc</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Jubilee hose clip assortment - 10 pc fuel line/diesel/petrol/coolant clamp packs x3</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>2390</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Daraz / Gravax corporation</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>gmail_msg_19de62bcdb1080ff|gmail_order_242365766580938</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-06 to 2026-05-08. Three 10 pc clamp packs at PKR 750 each; subtotal PKR 2250 plus PKR 140 shipping. Supplemental clamp stock only; does not close fuel-rated hose/clamp kit until sizes and clamp type are validated. Product links: https://www.daraz.pk/products/i645582306-s3011629985.html?urlFlag=true&amp;mp=1 ; https://www.daraz.pk/products/i645582306-s3011629988.html?urlFlag=true&amp;mp=1 ; https://www.daraz.pk/products/i645582306-s3011629989.html?urlFlag=true&amp;mp=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>part_mech_radiator_hose_set</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Radiator hose set upper plus lower with clamps</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Spec ready: order lines RPO-COOL-001 and RPO-COOL-002 define 2H/HJ47 molded EPDM coolant hoses, upper Toyota 16571-68020 / Dayco DMH1342 or CH1342 and lower Toyota 16572-68020. Complete RPA-002 neck measurements before payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>tool_daraz_safety_goggles_cleanup</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Safety goggles / protective glasses for grinding and cleaning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>764</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Daraz / Reliable_Shop</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>gmail_msg_19de62bcddc3ff3a|gmail_order_242365766080938</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Safety protective glasses x1; subtotal PKR 599 plus PKR 165 shipping. Product link: https://www.daraz.pk/products/i649346371-s3029400460.html?urlFlag=true&amp;mp=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Seam sealer</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>7696</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link. Gmail Autohub order 1761310 confirms 3x HB BODY 999 seam sealer and shipment status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>part_mech_spark_plugs_set</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Spark plugs set</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>not_required</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>not_required_diesel_engine</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; replaced in active baseline by diesel heat/glow plugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; quantity 2 pairs at PKR 9600 each, four stands total for chassis support. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; one of 9 physical items in PKR 94510 order for chassis lift/clean/suspension work. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>part_mech_vacuum_hose_refresh</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Vacuum hose refresh kit</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Spec ready: order lines RPO-VAC-001A through RPO-VAC-001C define reinforced 10-12 mm vacuum hose working basis, 16-19 mm oil-resistant breather basis, and Toyota/OEM 90923-02079 only if fitted. Complete RPA-009 before payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; hammer and dolly set for aluminium/body panel shaping. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>tool_wadfow_pressure_sprayer_wrs1550</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Wadfow Pressure sprayer WRS1550</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>goods</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>pending_delivery</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>ordered_pending_delivery</t>
         </is>
       </c>
-      <c r="I77" s="5" t="n">
+      <c r="I88" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Toolsmart.pk</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Paid Toolsmart order dated 2026-05-01; 5L sprayer for water-based degreaser application during chassis/engine/transmission cleaning.</t>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; 5L sprayer for water-based degreaser application during chassis/engine/transmission cleaning. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M77"/>
+  <autoFilter ref="A1:M88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6710,19 +7721,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
@@ -6853,123 +7864,135 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>part_mech_accessory_belt_set</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>tool_daraz_mini_wire_brush_set_x2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Accessory belt set</t>
+          <t>3 pc mini wire brush set - brass, nylon, stainless steel bristles x2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" s="5" t="n">
+        <v>561</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Bunyad Collection (Karachi)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>gmail_msg_19de62bcd140fa41|gmail_order_242365766980938</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_large_power</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>tool_daraz_75mm_knotted_cup_wire_brush_x2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
+          <t>75mm 3 inch steel knotted cup rotary wire brush for angle grinder x2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" s="5" t="n">
+        <v>3896</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Al Rehman Mart (Lahore)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
+          <t>gmail_msg_19de62bcd3dd7207|gmail_order_242365766280938</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_small_medium</t>
+          <t>part_mech_accessory_belt_set</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
+          <t>Accessory belt set</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -7011,27 +8034,27 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
+          <t>part_firewall_grommet_set_large_power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7041,22 +8064,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -7066,20 +8089,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_android_unit</t>
+          <t>part_firewall_grommet_set_small_medium</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Android unit</t>
+          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -7111,37 +8134,37 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>SehgalMotors.PK</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>part_bed_lining</t>
+          <t>part_mech_air_filter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bed lining</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7151,22 +8174,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -7176,20 +8199,20 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>part_bedliner_sprays</t>
+          <t>part_android_unit</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bedliner sprays</t>
+          <t>Android unit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -7221,37 +8244,37 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>SehgalMotors.PK</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
+          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tool_bench_grinder</t>
+          <t>part_bed_lining</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bench grinder</t>
+          <t>Bed lining</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7261,7 +8284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7271,35 +8294,35 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_body_mount_hardware_kit</t>
+          <t>part_bedliner_sprays</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Body mount hardware kit bolts sleeves washers</t>
+          <t>Bedliner sprays</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -7341,27 +8364,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>part_body_mount_shim_pack</t>
+          <t>tool_bench_grinder</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Body mount shim and spacer pack</t>
+          <t>Bench grinder</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7371,7 +8394,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -7381,42 +8404,42 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
+          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_body_mount_rubber_kit</t>
+          <t>part_body_mount_hardware_kit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Body-to-chassis mount rubber kit</t>
+          <t>Body mount hardware kit bolts sleeves washers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7426,7 +8449,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -7441,7 +8464,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -7451,27 +8474,27 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>part_cable_sleeve_protection</t>
+          <t>part_body_mount_shim_pack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
+          <t>Body mount shim and spacer pack</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7481,52 +8504,52 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / HAQ ELECTRIC</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
+          <t>part_body_mount_rubber_kit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Body-to-chassis mount rubber kit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7536,7 +8559,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7551,7 +8574,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -7561,20 +8584,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tool_cover</t>
+          <t>part_cable_sleeve_protection</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -7591,12 +8614,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7611,32 +8634,32 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>electronicsstore.pk / HAQ ELECTRIC</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>part_carpet</t>
+          <t>part_mech_brake_flex_hose_set</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carpet</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7646,7 +8669,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7661,7 +8684,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7671,27 +8694,27 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>part_mech_clutch_master_slave_refresh</t>
+          <t>tool_cover</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Clutch master and slave cylinder refresh kit</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7701,52 +8724,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
+          <t>part_carpet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Carpet</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7756,112 +8779,104 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>part_autohub_diss_apc_cleaner_5l</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>part_mech_clutch_master_slave_refresh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DISS (APC) All Purpose Cleaner 5L</t>
+          <t>Clutch master and slave cylinder refresh kit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" s="5" t="n">
-        <v>4999</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>part_dielectric_grease</t>
+          <t>part_copper_grease</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dielectric grease</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" s="5" t="n">
-        <v>5609</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>received</t>
@@ -7869,17 +8884,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7894,89 +8909,91 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Adenwalla &amp; Sons</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" s="5" t="n">
+        <v>4999</v>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>part_electric_wires</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
+          <t>part_dielectric_grease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
-        <v>11529</v>
+        <v>5609</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8010,48 +9027,42 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
-        <v>8811</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -8061,29 +9072,29 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
+          <t>part_electric_wires</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8093,16 +9104,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>7860</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" s="5" t="n">
+        <v>11529</v>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8112,49 +9123,55 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>part_mech_engine_mount_set</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>tool_electrical_test_kit</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Engine mount set</t>
+          <t>Electrical test kit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" s="5" t="n">
+        <v>8811</v>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>planned</t>
@@ -8162,7 +9179,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8187,42 +9204,48 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>part_mech_engine_oil_filter_service</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>quote_rubber_grommet_set_chat</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Engine oil + oil filter service pack</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Electrical wire grommet set (200pcs)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>7860</v>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -8237,30 +9260,30 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>fj40-00276</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
+          <t>part_mech_engine_mount_set</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Engine mount set</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -8302,31 +9325,27 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>part_evaporust_5l</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>part_mech_engine_oil_filter_service</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
+          <t>Engine oil + oil filter service pack</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8336,100 +9355,106 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7mart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>part_foam</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>tool_autohub_engine_detailing_brush_bundle_62191</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Engine/detailing brush bundle - tire sidewall brush, large detailing brush, 5 pc detailing brush set</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>2588</v>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>gmail_msg_19de62cf4907c036|gmail_order_1762191|autohub_order_62191</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
+          <t>part_epoxy_primer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -8461,7 +9486,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -8471,27 +9496,31 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>part_evaporust_5l</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8501,113 +9530,107 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>part_foam</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>3250</v>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
+          <t>part_mech_fuel_filter</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8617,119 +9640,113 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>part_h4_ceramic_headlight_connector_high</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>part_mech_fuel_hose_and_clamps</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>H4 ceramic headlight connectors - x4 received</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" s="5" t="n">
-        <v>1350</v>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Auto Xpert Pakistan</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tool_harden_3ton_trolley_jack_730213</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>54450</v>
+        <v>3250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8739,7 +9756,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8749,109 +9766,103 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tool_harden_spring_clamp_set_4in_6pc</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>tool_grease_gun</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>1200</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tool_harden_white_rubber_mallet_700g_590437</t>
+          <t>part_h4_ceramic_headlight_connector_high</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
+          <t>H4 ceramic headlight connectors - x4 received</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>2380</v>
+        <v>1350</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8861,7 +9872,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -8871,47 +9882,53 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>part_mech_heat_glow_plugs_set</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Heat/glow plugs set - diesel 2H</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>54450</v>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>new_only_planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -8921,157 +9938,169 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>1200</v>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_hidden_diesel_cutoff_switch</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hidden diesel cutoff switch (binary toggle)</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" s="5" t="n">
+        <v>2380</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
+          <t>part_mech_heat_glow_plugs_set</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Heat/glow plugs set - diesel 2H</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>new_only_planned</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9081,7 +10110,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -9106,38 +10135,32 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_heater_hose_set</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>2050</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -9147,51 +10170,47 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_ironman_front_dampers_separate_shipment</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_hidden_diesel_cutoff_switch</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+          <t>Hidden diesel cutoff switch (binary toggle)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -9201,7 +10220,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -9211,164 +10230,164 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_ironman_foamcell_suspension_kit</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_horn_relay</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>575000</v>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>tool_powerhouse_ingco_wb30501_wire_cup_brush_x3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>INGCO WB30501 Wire Cup Brush x3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" s="5" t="n">
+        <v>1065</v>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Powerhouse Express</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>gmail_msg_19de632df983464c|gmail_order_26242</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New battery purchase - installed</t>
+          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>20000</v>
+        <v>2050</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -9378,7 +10397,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -9388,45 +10407,43 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>part_ironman_front_dampers_separate_shipment</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>2188</v>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>ordered</t>
@@ -9434,7 +10451,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -9444,7 +10461,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -9459,46 +10476,48 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg</t>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>credit_old_battery_return</t>
+          <t>part_ironman_foamcell_suspension_kit</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Old battery return credit</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" s="5" t="n">
+        <v>575000</v>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>disputed</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -9508,97 +10527,103 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>akber_khan-00760|user_update_2026-05-01_battery_credit_wrong</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>part_daraz_jubilee_hose_clip_assortment_30pc</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Jubilee hose clip assortment - 10 pc fuel line/diesel/petrol/coolant clamp packs x3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" s="5" t="n">
+        <v>2390</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Gravax corporation</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>gmail_msg_19de62bcdb1080ff|gmail_order_242365766580938</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
+          <t>part_metal_protection</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -9608,7 +10633,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -9618,152 +10643,164 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_primer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>part_battery_purchase</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>20000</v>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>2188</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg|gmail_msg_19dd86b5fbb89675|gmail_delivery_241938794080938</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
+          <t>part_piano_hinge</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -9773,22 +10810,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -9798,31 +10835,27 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>part_power_steering_upgrade</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -9832,106 +10865,100 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>part_primer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>7696</v>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -9963,7 +10990,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -9973,27 +11000,27 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -10003,7 +11030,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -10018,7 +11045,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -10028,27 +11055,27 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_rear_axle_hard_brake_lines</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Rear axle hard brake lines and fittings</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -10058,7 +11085,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -10068,12 +11095,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -10083,27 +11110,27 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>BR-REAR-002|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
+          <t>part_rear_brake_line_cable_clips</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
+          <t>Rear brake line clips and parking-brake cable retainers</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -10113,52 +11140,52 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>BR-REAR-006|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
+          <t>part_rear_brake_shoes_hardware</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
+          <t>Rear brake shoes and spring hardware set</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -10168,52 +11195,52 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>inspect_then_buy</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>BR-REAR-005|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_rear_center_brake_flex_hose</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
+          <t>Rear center frame-to-axle flexible brake hose</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -10223,45 +11250,45 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>BR-REAR-003|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>part_rear_parking_brake_cable_set</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Rear parking brake cable set with clips and equalizer hardware</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -10293,7 +11320,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -10303,20 +11330,20 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>BR-REAR-001|20260501_194305_gp_EllBGvXA|20260501_194322_gp_XuRtjN4w</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_rear_wheel_cylinders_pair</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Rear wheel cylinders pair with bleed screws</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -10348,7 +11375,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>inspect_then_buy</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -10358,20 +11385,24 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>BR-REAR-004|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -10388,12 +11419,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -10408,97 +11439,109 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>tool_daraz_safety_goggles_cleanup</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Safety goggles / protective glasses for grinding and cleaning</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>764</v>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Reliable_Shop</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>gmail_msg_19de62bcddc3ff3a|gmail_order_242365766080938</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>7696</v>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -10508,164 +11551,152 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_self_etching_primer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>19200</v>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tool_total_wrecking_bar_600mm_tht431242</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_sound_dampening_sheets</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Total Wrecking bar 600mm THT431242</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>2860</v>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_mech_spark_plugs_set</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Spark plugs set</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -10675,7 +11706,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -10685,12 +11716,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -10700,43 +11731,37 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_split_conduit_braided_sleeve_medium</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>9870</v>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -10746,58 +11771,52 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_split_conduit_braided_sleeve_large</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wadfow Pressure sprayer WRS1550</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>2500</v>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -10807,42 +11826,42 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>part_split_conduit_braided_sleeve_small</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10852,45 +11871,45 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -10922,22 +11941,651 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>part_star_washers</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Star washers (bite into metal)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>tool_tap_set</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tap set</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>ToolsMart.pk</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>part_mech_thermostat_gasket</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Thermostat plus gasket</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>tool_torque_wrench</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Torque wrench</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>registered_needs_confirmation</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>ToolsMart.pk</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00395</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>part_mech_vacuum_hose_refresh</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Vacuum hose refresh kit</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>spec_ready</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Wadfow Pressure sprayer WRS1550</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>part_wax_and_grease_remover</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Wax and grease remover</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>next_phase_purchase</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Autohub</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>part_winch_switch</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Winch switch</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>deferred_optional</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>TBD (confirm)</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M74"/>
+  <autoFilter ref="A1:M85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/manual/j40-master-tracker.xlsx
+++ b/data/manual/j40-master-tracker.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Initial Price'!$A$1:$K$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Registration'!$A$1:$M$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Purchase of Goods'!$A$1:$M$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Purchase of Services'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-02 06:35:27</t>
+          <t>2026-05-02 09:05:53</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg|user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2326,8 +2326,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
@@ -2405,13 +2405,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>part_cable_sleeve_protection</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>part_bedliner_sprays</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
+          <t>Bedliner sprays</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2447,34 +2451,30 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / HAQ ELECTRIC</t>
+          <t>U-POL / Raptor on hand</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|user_shelf_image_2026-05-02_raptor_liner_visible</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Workbook inventory shows braided sleeve stock already received/paid: 8, 10, 14, 16, and 20 mm sleeve entries in 5m lengths. Audit physical quantities before any top-up.</t>
+          <t>Listed by the user as still needed; chat says they are required immediately after floor repair and primer | Marked on hand from shelf image on 2026-05-02: Raptor liner bottles visible. Treat as bedliner/protective coating already acquired, not as primer.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>part_autohub_diss_apc_cleaner_5l</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>part_cable_sleeve_protection</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DISS (APC) All Purpose Cleaner 5L</t>
+          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2502,9 +2502,7 @@
           <t>received</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
-        <v>4999</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2512,30 +2510,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>electronicsstore.pk / HAQ ELECTRIC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
+          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
+          <t>Workbook inventory shows braided sleeve stock already received/paid: 8, 10, 14, 16, and 20 mm sleeve entries in 5m lengths. Audit physical quantities before any top-up.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>part_dielectric_grease</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dielectric grease</t>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2564,7 +2566,7 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>5609</v>
+        <v>4999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2573,34 +2575,30 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Adenwalla &amp; Sons</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx. Gmail AliExpress evidence shows dielectric grease order 3070231697777489 shipped and package PK001206015RS delivered.</t>
+          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>part_electric_wires</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
+          <t>part_dielectric_grease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2629,7 +2627,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>11529</v>
+        <v>5609</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2638,34 +2636,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Received AliExpress order 3070027285627489: 4 AWG silicone cable, red/black, 1m each (approx 21 mm2). Workbook also contains 1.0/1.5/2.5 mm2 roll inventory; physically count before buying more wire.</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx. Gmail AliExpress evidence shows dielectric grease order 3070231697777489 shipped and package PK001206015RS delivered.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
+          <t>part_electric_wires</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
+          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2694,7 +2692,7 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>3250</v>
+        <v>11529</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2703,34 +2701,30 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
+          <t>Received AliExpress order 3070027285627489: 4 AWG silicone cable, red/black, 1m each (approx 21 mm2). Workbook also contains 1.0/1.5/2.5 mm2 roll inventory; physically count before buying more wire.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_h4_ceramic_headlight_connector_high</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>part_hidden_diesel_cutoff_switch</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>H4 ceramic headlight connectors - x4 received</t>
+          <t>Fuel stop switch / hidden diesel cutoff (needle-type switch)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2758,9 +2752,7 @@
           <t>received</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>1350</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2768,34 +2760,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Auto Xpert Pakistan</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
+          <t>user_image_2026-03-21_electrical_leftovers|photo_20260420_221819_gp_YV69fbvA|photo_20260421_194401_gp_1dY3fLdw|user_update_2026-05-02_parts_review</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>User has 4 H4 ceramic headlight connectors received. Only 2 are required for the headlights, leaving 2 spares; no additional H4 connectors are required.</t>
+          <t>User confirmed the fuel stop switch is already purchased; simple needle-type switch visible in the April 20/21 control photos.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New battery purchase - installed</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2815,16 +2807,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>20000</v>
+        <v>3250</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2833,34 +2825,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>New battery is already purchased and installed. Gross PKR 20,000 retained.</t>
+          <t>User-provided order confirmation email: order 62074 placed 2026-04-27; delivery window 2-3 working days. User update 2026-04-29: cleaner parts arrived.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>part_h4_ceramic_headlight_connector_high</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>H4 ceramic headlight connectors - x4 received</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2889,7 +2881,7 @@
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2188</v>
+        <v>1350</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2898,34 +2890,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg|gmail_msg_19dd86b5fbb89675|gmail_delivery_241938794080938</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Daraz order 241938794080938 was delivered per Gmail delivery confirmation dated 2026-04-29. Original order matched exact item + quantity (2) and total PKR 2188.</t>
+          <t>User has 4 H4 ceramic headlight connectors received. Only 2 are required for the headlights, leaving 2 spares; no additional H4 connectors are required.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
+          <t>part_battery_purchase</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2945,15 +2937,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>received</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>20000</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -2961,30 +2955,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html. User correction 2026-05-01: current tracker image is incorrect; require exact order/received photo before treating image as evidence.</t>
+          <t>New battery is already purchased and installed. Gross PKR 20,000 retained.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3012,7 +3010,9 @@
           <t>received</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" s="5" t="n">
+        <v>2188</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3020,30 +3020,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg|gmail_msg_19dd86b5fbb89675|gmail_delivery_241938794080938</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (14mm and 16mm, 5m lengths). No additional medium sleeve required until physical count shows a gap.</t>
+          <t>Daraz order 241938794080938 was delivered per Gmail delivery confirmation dated 2026-04-29. Original order matched exact item + quantity (2) and total PKR 2188.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3079,30 +3083,30 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (20mm, 5m lengths). No additional large sleeve required until physical count shows a gap.</t>
+          <t>User confirmed this grommet set was received; exact product link: https://www.aliexpress.com/i/1005008318051049.html. User correction 2026-05-01: current tracker image is incorrect; require exact order/received photo before treating image as evidence.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3148,29 +3152,25 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Covered by received workbook sleeve inventory (8mm and 10mm, 5m lengths). No additional small sleeve required until physical count shows a gap.</t>
+          <t>Covered by received workbook sleeve inventory (14mm and 16mm, 5m lengths). No additional medium sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>admin_excise_challan</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>part_split_conduit_braided_sleeve_large</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Excise challan</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3185,17 +3185,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>11365</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3203,39 +3201,35 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Vehicle transfer cost mentioned in the group chat</t>
+          <t>Covered by received workbook sleeve inventory (20mm, 5m lengths). No additional large sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>admin_vehicle_purchase</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>part_split_conduit_braided_sleeve_small</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vehicle purchase price</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3250,12 +3244,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3266,58 +3260,64 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>seller</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>fj40-00014</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
+          <t>Covered by received workbook sleeve inventory (8mm and 10mm, 5m lengths). No additional small sleeve required until physical count shows a gap.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>admin_excise_challan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Excise challan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>received</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>11365</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3325,55 +3325,59 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
+          <t>Vehicle transfer cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tool_cover</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>admin_vehicle_purchase</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Vehicle purchase price</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3384,30 +3388,30 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>seller</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>fj40-00014</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
+          <t>Chat confirms the jeep was bought but the exact purchase price is not yet captured in the archive</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
+          <t>part_mech_air_filter</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3443,34 +3447,30 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked received per user confirmation; fitment/condition can be validated during installation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>part_evaporust_5l</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>tool_cover</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3506,30 +3506,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7mart</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
+          <t>Marked with x in the user purchase list; chat shows it was needed before strip-down, was already on the way on 2026-03-17, budget guidance was 2-4k, and arrival was confirmed on 2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
+          <t>part_copper_grease</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3565,30 +3565,34 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_seed</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
+          <t>Marked with x in the user purchase list Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>part_hidden_diesel_cutoff_switch</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>part_evaporust_5l</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hidden diesel cutoff switch (binary toggle)</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3624,30 +3628,30 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Identified from latest photo batch as the likely hidden diesel cutoff switch; marked received per user confirmation</t>
+          <t>Marked delivered per user confirmation; this was previously tracked as quote/pending against INV-0031</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
+          <t>tool_grease_gun</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3683,30 +3687,30 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Listed with Y in the user purchase list</t>
+          <t>Seeded as received; a later tool basket shows a Harden Pro Grease Gun 500CC at Rs.4,790 and tools later arrived, but the exact paid amount is still left open pending order proof</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
+          <t>part_piano_hinge</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3742,30 +3746,30 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_seed</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; tap set was later discussed as useful for stripped bolts Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Listed with Y in the user purchase list</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
+          <t>tool_tap_set</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Tap set</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3801,30 +3805,30 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Marked received per user confirmation; compatibility/usability can be validated during install planning</t>
+          <t>Marked with x in the user purchase list; tap set was later discussed as useful for stripped bolts Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
+          <t>part_mech_thermostat_gasket</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Thermostat plus gasket</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3860,39 +3864,35 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Marked with x in the user purchase list; torque wrench was explicitly called out in tool planning chat Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Marked received per user confirmation; compatibility/usability can be validated during install planning</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>admin_vehicle_inspection</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>tool_torque_wrench</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vehicle inspection</t>
+          <t>Torque wrench</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>goods</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3902,22 +3902,20 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>received</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>5000</v>
-      </c>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -3925,63 +3923,63 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Fj40 group</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>fj40-00025</t>
+          <t>user_seed|akber_khan-00395</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Inspection cost mentioned in the group chat</t>
+          <t>Marked with x in the user purchase list; torque wrench was explicitly called out in tool planning chat Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
+          <t>admin_vehicle_inspection</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
+          <t>Vehicle inspection</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>goods</t>
+          <t>services</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>7860</v>
+        <v>5000</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -3990,30 +3988,34 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>Fj40 group</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>fj40-00025</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Reference quote only; duplicate path now superseded by the received AliExpress grommet set Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Inspection cost mentioned in the group chat</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tool_breaker_bar</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>quote_rubber_grommet_set_chat</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1/2 inch 24 inch breaker bar, heavy duty</t>
+          <t>Electrical wire grommet set (200pcs)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4023,7 +4025,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4038,10 +4040,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>deferred_optional</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>7860</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -4049,30 +4053,30 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00346</t>
+          <t>fj40-00276</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; breaker bar was part of the minimum tool list discussed around steering work</t>
+          <t>Reference quote only; duplicate path now superseded by the received AliExpress grommet set Vendor backfilled from J40_Costs.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>part_mech_accessory_belt_set</t>
+          <t>tool_breaker_bar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accessory belt set</t>
+          <t>1/2 inch 24 inch breaker bar, heavy duty</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4097,7 +4101,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4108,30 +4112,30 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>local</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00346</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Listed by the user as still needed; breaker bar was part of the minimum tool list discussed around steering work</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_large_power</t>
+          <t>part_mech_accessory_belt_set</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
+          <t>Accessory belt set</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4172,25 +4176,25 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Large pass-through sizes still needed for protected heavy feed runs and split-loom trunk crossings</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_small_medium</t>
+          <t>part_firewall_grommet_set_large_power</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
+          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4231,25 +4235,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Additional small and medium pass-through sizes still needed to cover loom branch and signal wire firewall exits</t>
+          <t>Large pass-through sizes still needed for protected heavy feed runs and split-loom trunk crossings</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>part_android_unit</t>
+          <t>part_firewall_grommet_set_small_medium</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Android unit</t>
+          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4274,7 +4278,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4285,30 +4289,30 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SehgalMotors.PK</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9 inch, flush-mounted, integrated into the dash panel; later shopping basket includes a priced Android unit candidate Vendor backfilled from J40_Costs.xlsx.</t>
+          <t>Additional small and medium pass-through sizes still needed to cover loom branch and signal wire firewall exits</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>part_bed_lining</t>
+          <t>part_android_unit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bed lining</t>
+          <t>Android unit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4333,7 +4337,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4344,30 +4348,30 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>SehgalMotors.PK</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280|user_update_2026-05-02_dashboard_switch_lcd_update</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat sequences this after welding/primer and before sound deadening</t>
+          <t>9 inch, flush-mounted, integrated into the dash panel. User update 2026-05-02: a specific 9 inch LCD panel has been recommended; capture exact model/link, dimensions, mounting depth, power draw, and camera inputs before purchase. Keep deferred_optional until baseline dash/electrical fit-up is proven.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>part_bedliner_sprays</t>
+          <t>part_bed_lining</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bedliner sprays</t>
+          <t>Bed lining</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4392,7 +4396,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4408,12 +4412,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat says they are required immediately after floor repair and primer</t>
+          <t>Listed by the user as still needed; chat sequences this after welding/primer and before sound deadening</t>
         </is>
       </c>
     </row>
@@ -4721,13 +4725,13 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
+          <t>part_foam</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4752,7 +4756,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4773,20 +4777,20 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>part_foam</t>
+          <t>part_mech_fuel_filter</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4811,7 +4815,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4827,25 +4831,29 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit interior finish-stack mention in chat</t>
+          <t>MECH BASELINE MUST REPLACE during full restore</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>part_suspension_wooden_cribbing_blocks</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
+          <t>Hardwood cribbing / wooden support blocks for suspension replacement - 12 piece working set</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4881,30 +4889,30 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>local timber / hardware supplier</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_update_2026-05-02_suspension_wooden_blocks</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>MECH BASELINE MUST REPLACE during full restore</t>
+          <t>Add for Ironman suspension replacement support setup. Working order: 12 solid hardwood/timber pieces total, expected as 8 cribbing blocks plus 4 wedge chocks or equivalent mechanic-approved mix. Use only sound, dry, square-cut hardwood/timber with broad bearing faces; reject cracked, soft, split, oily, or uneven offcuts. These supplement jack stands and axle support during leaf spring/shock work and are not a substitute for rated stands. Confirm final dimensions with the workshop before purchase.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4945,25 +4953,25 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; baseline electrical reliability item</t>
+          <t>Spec: Toyota radiator cap 16401-41021 or exact pressure-equivalent cap for the fitted radiator neck; replace with coolant hose service.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
+          <t>part_rear_axle_hard_brake_lines</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Rear axle hard brake lines and fittings</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4988,7 +4996,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,30 +5007,30 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>BR-REAR-002|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed</t>
+          <t>Recreate left/right rear axle lines in brake-rated 3/16 in / 4.75 mm tube after flare standard, fitting threads, bend templates, and clip positions are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_primer</t>
+          <t>part_rear_brake_line_cable_clips</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Rear brake line clips and parking-brake cable retainers</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5047,7 +5055,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5063,25 +5071,25 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>BR-REAR-006|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research</t>
+          <t>Count and replace corroded or missing brake-line clips, cable retainers, rubber sleeves, grommets, and rubber-lined P-clips before final rear axle routing.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
+          <t>part_rear_brake_shoes_hardware</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Rear brake shoes and spring hardware set</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5106,7 +5114,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>inspect_then_buy</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,25 +5130,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>BR-REAR-005|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Spec: Toyota radiator cap 16401-41021 or exact pressure-equivalent cap for the fitted radiator neck; replace with coolant hose service.</t>
+          <t>Order shoes, return springs, hold-down springs, adjusters, and retainers after drum diameter, shoe width, and backing-plate family are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>part_rear_axle_hard_brake_lines</t>
+          <t>part_rear_center_brake_flex_hose</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rear axle hard brake lines and fittings</t>
+          <t>Rear center frame-to-axle flexible brake hose</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5181,25 +5189,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BR-REAR-002|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
+          <t>BR-REAR-003|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Recreate left/right rear axle lines in brake-rated 3/16 in / 4.75 mm tube after flare standard, fitting threads, bend templates, and clip positions are confirmed.</t>
+          <t>Replace rear center hose once chassis-side and axle-side fitting threads/end styles and full-droop slack are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_rear_brake_line_cable_clips</t>
+          <t>part_rear_parking_brake_cable_set</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rear brake line clips and parking-brake cable retainers</t>
+          <t>Rear parking brake cable set with clips and equalizer hardware</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5240,25 +5248,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BR-REAR-006|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
+          <t>BR-REAR-001|20260501_194305_gp_EllBGvXA|20260501_194322_gp_XuRtjN4w</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Count and replace corroded or missing brake-line clips, cable retainers, rubber sleeves, grommets, and rubber-lined P-clips before final rear axle routing.</t>
+          <t>Replace the rear handbrake/parking-brake cable system as a safety baseline; order only after cable end types, lengths, equalizer hardware, and backing-plate levers are confirmed from the removed samples.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_rear_brake_shoes_hardware</t>
+          <t>part_rear_wheel_cylinders_pair</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rear brake shoes and spring hardware set</t>
+          <t>Rear wheel cylinders pair with bleed screws</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5299,25 +5307,25 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BR-REAR-005|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
+          <t>BR-REAR-004|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Order shoes, return springs, hold-down springs, adjusters, and retainers after drum diameter, shoe width, and backing-plate family are confirmed.</t>
+          <t>Buy as a left/right pair after drum opening confirms cylinder bore, port thread, mounting pattern, and pushrod style.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_rear_center_brake_flex_hose</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rear center frame-to-axle flexible brake hose</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5342,7 +5350,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>spec_needed_before_order</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5358,25 +5366,25 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BR-REAR-003|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Replace rear center hose once chassis-side and axle-side fitting threads/end styles and full-droop slack are confirmed.</t>
+          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_rear_parking_brake_cable_set</t>
+          <t>part_power_steering_upgrade</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rear parking brake cable set with clips and equalizer hardware</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5386,7 +5394,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5396,12 +5404,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>spec_needed_before_order</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5417,25 +5425,29 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BR-REAR-001|20260501_194305_gp_EllBGvXA|20260501_194322_gp_XuRtjN4w</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Replace the rear handbrake/parking-brake cable system as a safety baseline; order only after cable end types, lengths, equalizer hardware, and backing-plate levers are confirmed from the removed samples.</t>
+          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_rear_wheel_cylinders_pair</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>tool_daraz_mini_wire_brush_set_x2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rear wheel cylinders pair with bleed screws</t>
+          <t>3 pc mini wire brush set - brass, nylon, stainless steel bristles x2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5445,25 +5457,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>inspect_then_buy</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>561</v>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5471,30 +5485,34 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Bunyad Collection (Karachi)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BR-REAR-004|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
+          <t>gmail_msg_19de62bcd140fa41|gmail_order_242365766980938</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Buy as a left/right pair after drum opening confirms cylinder bore, port thread, mounting pattern, and pushrod style.</t>
+          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Two 3 pc mini wire brush sets at PKR 198 each; subtotal PKR 396 plus PKR 165 shipping. Product link: https://www.daraz.pk/products/i192752152-s1385484991.html?urlFlag=true&amp;mp=1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>part_wax_and_grease_remover</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>3M Prep Solvent-70 1 gallon / wax and grease remover</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5504,22 +5522,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5530,30 +5548,34 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00817|user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; explicit bodywork-material mention in chat</t>
+          <t>Listed by the user as still needed; later product research includes an Autohub remover link | User confirmed Autohub prep solvent ordered and paid on 2026-05-02. Exact invoice amount/order number still to be reconciled from receipt. Link: https://autohub.pk/products/3m-prep-solvent-70-1-gallon</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>tool_daraz_75mm_knotted_cup_wire_brush_x2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>75mm 3 inch steel knotted cup rotary wire brush for angle grinder x2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5563,25 +5585,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>3896</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5589,30 +5613,30 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Al Rehman Mart (Lahore)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>gmail_msg_19de62bcd3dd7207|gmail_order_242365766280938</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; repeatedly discussed as part of the proper floor/cabin sequence</t>
+          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Quantity 2 at PKR 1878 each; subtotal PKR 3756 plus PKR 140 shipping. Product link: https://www.daraz.pk/products/i2171955-s1269424717.html?urlFlag=true&amp;mp=1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
+          <t>tool_bench_grinder</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Bench grinder</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5622,7 +5646,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5632,12 +5656,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5648,30 +5672,30 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; accessory-control switch, not treated as immediate baseline until lighting layout is locked</t>
+          <t>User update 2026-04-27: bench grinder currently considered not required.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_body_mount_hardware_kit</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Body mount hardware kit bolts sleeves washers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5681,7 +5705,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5696,7 +5720,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5712,25 +5736,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points</t>
+          <t>Spec ready: sleeves 8 blanks; cups 14; M10 trial bolts 16; nuts washers and repair pack defined. Complete BMA-006/BMA-007 before final sleeve cutting and bolt length selection. Millat bolt/nut/washer subset is now tracked separately in part_fastener_kit_a_millat; this row remains release-held for sleeves, cups, captive-thread repair material, and final bolt-length validation.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>part_body_mount_shim_pack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Body mount shim and spacer pack</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5740,7 +5764,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5755,7 +5779,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -5766,30 +5790,30 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub remover link</t>
+          <t>Spec ready: thin shim pack 1/2/3/5 mm x12 each plus thick control pack 5/10/15 mm x4 each. Complete BMA-008 station measurement before final use.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_winch_switch</t>
+          <t>part_body_mount_rubber_kit</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Winch switch</t>
+          <t>Body-to-chassis mount rubber kit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5799,7 +5823,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5814,7 +5838,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -5830,25 +5854,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Added from the user-provided remaining electrical-items screenshot; keep out of baseline electrical buys unless the winch path is confirmed</t>
+          <t>Spec ready with quantities in body_mount_order_release_specs.csv; complete BMA-001/BMA-002 route decision before committing purchase.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
+          <t>part_mech_brake_flex_hose_set</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5858,7 +5882,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5868,12 +5892,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -5889,29 +5913,25 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_plan_2026-04-12_engine_bay_review|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Upgrade path under consideration; leave behind the steering decision gate until the baseline inspection is complete</t>
+          <t>Spec ready: order line RPO-BRAKE-001A defines brake-fluid-rated flex hoses matched to current front/rear fittings plus free/full-droop length in mm. Complete RPA-006 fitting photos and full-droop slack check before payment.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tool_daraz_mini_wire_brush_set_x2</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3 pc mini wire brush set - brass, nylon, stainless steel bristles x2</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5926,22 +5946,20 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>561</v>
-      </c>
+          <t>not_required_diesel_engine</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -5949,24 +5967,24 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Daraz / Bunyad Collection (Karachi)</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62bcd140fa41|gmail_order_242365766980938</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Two 3 pc mini wire brush sets at PKR 198 each; subtotal PKR 396 plus PKR 165 shipping. Product link: https://www.daraz.pk/products/i192752152-s1385484991.html?urlFlag=true&amp;mp=1</t>
+          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; no distributor ignition tune-up item required.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tool_daraz_75mm_knotted_cup_wire_brush_x2</t>
+          <t>tool_autohub_engine_detailing_brush_bundle_62191</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5976,7 +5994,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>75mm 3 inch steel knotted cup rotary wire brush for angle grinder x2</t>
+          <t>Engine/detailing brush bundle - tire sidewall brush, large detailing brush, 5 pc detailing brush set</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6005,7 +6023,7 @@
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>3896</v>
+        <v>2588</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -6014,30 +6032,34 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Daraz / Al Rehman Mart (Lahore)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62bcd3dd7207|gmail_order_242365766280938</t>
+          <t>gmail_msg_19de62cf4907c036|gmail_order_1762191|autohub_order_62191</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Quantity 2 at PKR 1878 each; subtotal PKR 3756 plus PKR 140 shipping. Product link: https://www.daraz.pk/products/i2171955-s1269424717.html?urlFlag=true&amp;mp=1</t>
+          <t>Autohub order 1762191 / order number 62191 confirmed 2026-05-02: Tire Side Wall Cleaning Brush x1, Detailing Brush Large x1, 5 Pcs Detailing Brush Set x1; subtotal PKR 2339 plus PKR 249 shipping. Links: https://autohub.pk/products/tire-side-wall-cleaning-brush ; https://autohub.pk/products/detailing-brush-large-16-no ; https://autohub.pk/products/5-pcs-detailing-brush-set</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tool_bench_grinder</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>part_epoxy_primer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bench grinder</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6062,7 +6084,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>not_required_duplicate</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6073,30 +6095,34 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>Daraz / ICI Industrial Coatings</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_seed|akber_khan-00803|user_update_2026-05-02_zinc_rich_epoxy_primer_order</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>User update 2026-04-27: bench grinder currently considered not required.</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat | Closed on 2026-05-02: epoxy-primer need is covered by part_primer order for Hi-Build Zinc Rich Epoxy Primer EC 11; do not buy a second epoxy primer.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_body_mount_hardware_kit</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>part_fastener_kit_a_millat</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Body mount hardware kit bolts sleeves washers</t>
+          <t>Fastener Kit A: Tub-to-chassis mounts (OEM positions) - M10/M12 class 8.8 bolts, matching nuts, flat+spring washers, sleeves</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6111,17 +6137,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6132,30 +6158,34 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
+          <t>gmail_msg_19d9d26f415b48fa|gmail_msg_19d9cd91c8d55038|gmail_msg_19d9ce99ff7c3bab|gmail_msg_19db2d73afb4876e|gmail_msg_19db2d7aa7027a2c|gmail_msg_19dbc4673054004c|gmail_msg_19dbc462741aef46</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Spec ready: sleeves 8 blanks; cups 14; M10 trial bolts 16; nuts washers and repair pack defined. Complete BMA-006/BMA-007 before final sleeve cutting and bolt length selection.</t>
+          <t>Registered under paid MTL/Millat orders 38902 and 38903 from 2026-04-18. Gmail evidence shows both MTL order-received emails plus user payment follow-ups on 2026-04-22 and 2026-04-24. Covers the Millat M10/M12 bolt, nut, flat-washer, and lock-washer stock; sleeve/spacer cutting still waits for body-mount dry-stack measurements before final installation.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>part_body_mount_shim_pack</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>part_fastener_kit_b_millat</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Body mount shim and spacer pack</t>
+          <t>Fastener Kit B: Body panel/bracket hardware - M6/M8 class 8.8 flange bolts, nyloc nuts, washers</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6170,17 +6200,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6191,30 +6221,34 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
+          <t>gmail_msg_19d9d26f415b48fa|gmail_msg_19d9cd91c8d55038|gmail_msg_19d9ce99ff7c3bab|gmail_msg_19db2d73afb4876e|gmail_msg_19db2d7aa7027a2c|gmail_msg_19dbc4673054004c|gmail_msg_19dbc462741aef46</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Spec ready: thin shim pack 1/2/3/5 mm x12 each plus thick control pack 5/10/15 mm x4 each. Complete BMA-008 station measurement before final use.</t>
+          <t>Registered under paid MTL/Millat orders 38902 and 38903 from 2026-04-18. Covers the Millat M6/M8 bolt, nut, and washer portion of the body-panel/bracket hardware set. Receipt check still needs to verify exact lengths, quantities, and any local top-up for sizes that were not clean Millat matches.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>part_body_mount_rubber_kit</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>part_fastener_kit_d_millat</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Body-to-chassis mount rubber kit</t>
+          <t>Fastener Kit D: Grounding hardware - star/serrated washers M6/M8/M10 + cleaned contact points</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6229,17 +6263,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6250,30 +6284,30 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
+          <t>gmail_msg_19d9d26f415b48fa|gmail_msg_19d9cd91c8d55038|gmail_msg_19d9ce99ff7c3bab|gmail_msg_19db2d73afb4876e|gmail_msg_19db2d7aa7027a2c|gmail_msg_19dbc4673054004c|gmail_msg_19dbc462741aef46</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Spec ready with quantities in body_mount_order_release_specs.csv; complete BMA-001/BMA-002 route decision before committing purchase.</t>
+          <t>Registered under paid MTL/Millat orders 38902 and 38903 from 2026-04-18. Covers the ordered Millat washer/lock-washer stock used for grounding and vibration-resistant joints. Conductive paste and any non-Millat grounding top-up remain separate until physically confirmed.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
+          <t>part_mech_fuel_hose_and_clamps</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6314,25 +6348,29 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Spec ready: order line RPO-BRAKE-001A defines brake-fluid-rated flex hoses matched to current front/rear fittings and full-droop length. Complete RPA-006 fitting photos and full-droop slack check before payment.</t>
+          <t>Spec ready: order lines RPO-FUEL-001A through RPO-FUEL-001C define diesel-rated hose: 8 mm ID x 3000 mm feed, 6 mm ID x 2000 mm return, 3.2-3.5 mm ID x 1000 mm leak-off. Complete RPA-002/RPA-004 before payment. Do not fabricate high-pressure injector pipes.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>part_cavity_wax</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>HB Body U900 cavity wax spray 400ml</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6347,17 +6385,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -6368,34 +6406,34 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; no distributor ignition tune-up item required.</t>
+          <t>User confirmed Autohub cavity wax order paid on 2026-05-02. Recommended quantity was 2 spray cans; confirm invoice quantity and amount on receipt. Link: https://autohub.pk/products/hb-body-u900-cavity-wax-spray-u900-400ml</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tool_autohub_engine_detailing_brush_bundle_62191</t>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Engine/detailing brush bundle - tire sidewall brush, large detailing brush, 5 pc detailing brush set</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6424,7 +6462,7 @@
         </is>
       </c>
       <c r="I68" s="5" t="n">
-        <v>2588</v>
+        <v>54450</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -6433,30 +6471,34 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62cf4907c036|gmail_order_1762191|autohub_order_62191</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Autohub order 1762191 / order number 62191 confirmed 2026-05-02: Tire Side Wall Cleaning Brush x1, Detailing Brush Large x1, 5 Pcs Detailing Brush Set x1; subtotal PKR 2339 plus PKR 249 shipping. Links: https://autohub.pk/products/tire-side-wall-cleaning-brush ; https://autohub.pk/products/detailing-brush-large-16-no ; https://autohub.pk/products/5-pcs-detailing-brush-set</t>
+          <t>Paid Toolsmart order dated 2026-05-01; primary 3T trolley jack for lifting before supporting chassis on stands. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6471,20 +6513,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>1200</v>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -6492,24 +6536,24 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Spec ready: order lines RPO-FUEL-001A through RPO-FUEL-001C define diesel-rated SAE J30R9/J30R14T2 or DIN 73379-3E hose; 8 mm feed x3 m, 6 mm return x2 m, 3.2-3.5 mm leak-off x1 m. Complete RPA-002/RPA-004 before payment. Do not fabricate high-pressure injector pipes.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; clamp set for holding pads, small parts, and temporary setup during cleaning/bodywork. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tool_harden_3ton_trolley_jack_730213</t>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6519,7 +6563,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6548,7 +6592,7 @@
         </is>
       </c>
       <c r="I70" s="5" t="n">
-        <v>54450</v>
+        <v>2380</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6567,24 +6611,20 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; primary 3T trolley jack for lifting before supporting chassis on stands. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+          <t>Paid Toolsmart order dated 2026-05-01; soft mallet for non-marring persuasion and aluminium/bodywork shaping. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tool_harden_spring_clamp_set_4in_6pc</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_heat_glow_plugs_set</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
+          <t>Heat/glow plugs set - diesel 2H</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6599,22 +6639,20 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>1200</v>
-      </c>
+          <t>purchase_ready</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -6622,34 +6660,30 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; clamp set for holding pads, small parts, and temporary setup during cleaning/bodywork. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+          <t>Diesel baseline item. Buy NEW only; confirm fitted engine code plus current plug voltage/thread/reach or old plug part number before payment.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tool_harden_white_rubber_mallet_700g_590437</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_heater_hose_set</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6664,22 +6698,20 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>2380</v>
-      </c>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -6687,30 +6719,34 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; soft mallet for non-marring persuasion and aluminium/bodywork shaping. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+          <t>Spec ready: order lines RPO-COOL-004A and RPO-COOL-004B define EPDM SAE J20R3 heater hose, 400 mm inlet and 280 mm outlet cut lengths, expected 16 mm / 5/8 inch ID. Complete RPA-002 nipple measurements and rear-heater check before payment.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>part_mech_heat_glow_plugs_set</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>part_primer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Heat/glow plugs set - diesel 2H</t>
+          <t>Hi-Build Zinc Rich Epoxy Primer EC 11 two-pack set</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6725,17 +6761,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -6746,30 +6782,30 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / ICI Industrial Coatings</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819|user_update_2026-05-02_zinc_rich_epoxy_primer_order</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Diesel baseline item. Buy NEW only; confirm fitted engine code plus current plug voltage/thread/reach or old plug part number before payment.</t>
+          <t>Listed by the user as still needed; chat ties primer to floor spot-weld work and later product research | User confirmed ordered and paid on 2026-05-02. Selected as the zinc-rich two-pack epoxy primer for blasted steel chassis; seller images show separate base and hardener tins. Confirm mix ratio, thinner, and recoat window on receipt. Link: https://www.daraz.pk/products/ici-industrial-coating-zinc-rich-epoxy-primer-set-zinc-rich-primer-set-ici-industrial-i556870547.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
+          <t>part_horn_relay</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6784,17 +6820,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>not_required_duplicate</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -6810,12 +6846,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_image_2026-03-21_electrical_leftovers|electrical_master_T3|user_update_2026-05-02_parts_review</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Spec ready: order lines RPO-COOL-004A and RPO-COOL-004B define Toyota 99552-30500 L=400 and 99552-30300 L=280 or EPDM SAE J20R3 local hose, expected 16 mm / 5/8 inch ID. Complete RPA-002 nipple measurements and rear-heater check before payment.</t>
+          <t>Duplicate with the active/as-built T3 horn relay and existing relay stock; do not buy another horn relay unless functional testing shows a failed relay.</t>
         </is>
       </c>
     </row>
@@ -7145,13 +7181,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>part_metal_protection</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7171,12 +7211,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>not_required_covered_by_epoxy_wax</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -7187,34 +7227,30 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701|user_update_2026-05-02_zinc_rich_epoxy_primer_order|user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Spec ready: order lines RPO-COOL-001 and RPO-COOL-002 define 2H/HJ47 molded EPDM coolant hoses, upper Toyota 16571-68020 / Dayco DMH1342 or CH1342 and lower Toyota 16572-68020. Complete RPA-002 neck measurements before payment.</t>
+          <t>Listed by the user as still needed; rust reformer and related metal-treatment products were discussed | Closed on 2026-05-02 as a generic duplicate: current corrosion-protection stack is covered by zinc-rich epoxy primer, prep solvent, seam sealer, cavity wax, and on-hand Raptor bedliner.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>tool_daraz_safety_goggles_cleanup</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
+          <t>part_mech_radiator_hose_set</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Safety goggles / protective glasses for grinding and cleaning</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7229,22 +7265,20 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>764</v>
-      </c>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -7252,34 +7286,34 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Daraz / Reliable_Shop</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62bcddc3ff3a|gmail_order_242365766080938</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Safety protective glasses x1; subtotal PKR 599 plus PKR 165 shipping. Product link: https://www.daraz.pk/products/i649346371-s3029400460.html?urlFlag=true&amp;mp=1</t>
+          <t>Spec ready: order lines RPO-COOL-001 and RPO-COOL-002 define spec-led molded EPDM coolant hoses; Toyota/Dayco numbers are cross-references only. Record old-hose free lengths plus neck and clamp ODs in mm before payment.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
+          <t>tool_daraz_safety_goggles_cleanup</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Safety goggles / protective glasses for grinding and cleaning</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7294,7 +7328,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7308,7 +7342,7 @@
         </is>
       </c>
       <c r="I82" s="5" t="n">
-        <v>7696</v>
+        <v>764</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -7317,30 +7351,34 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Daraz / Reliable_Shop</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>gmail_msg_19de62bcddc3ff3a|gmail_order_242365766080938</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link. Gmail Autohub order 1761310 confirms 3x HB BODY 999 seam sealer and shipment status.</t>
+          <t>Daraz order confirmed 2026-05-02; delivery window 2026-05-05 to 2026-05-07. Safety protective glasses x1; subtotal PKR 599 plus PKR 165 shipping. Product link: https://www.daraz.pk/products/i649346371-s3029400460.html?urlFlag=true&amp;mp=1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7355,20 +7393,22 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>7696</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -7376,34 +7416,34 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg|user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; replaced in active baseline by diesel heat/glow plugs.</t>
+          <t>Listed by the user as still needed; later product research includes an Autohub seam-sealer link. Gmail Autohub order 1761310 confirms 3x HB BODY 999 seam sealer and shipment status. | Payment marked paid per user confirmation on 2026-05-02; keep delivery/quantity reconciliation tied to Autohub order 1761310 and physical tube count.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+          <t>part_self_etching_primer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7418,22 +7458,20 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>19200</v>
-      </c>
+          <t>not_required_with_epoxy</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -7441,34 +7479,30 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_seed|akber_khan-00803|user_update_2026-05-02_zinc_rich_epoxy_primer_order</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; quantity 2 pairs at PKR 9600 each, four stands total for chassis support. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+          <t>Listed by the user as still needed; explicit bodywork-material mention in chat | Closed on 2026-05-02: not ordering self-etch primer under the selected two-pack zinc-rich epoxy system unless that coating system later explicitly requires it.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tool_total_wrecking_bar_600mm_tht431242</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_spark_plugs_set</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Total Wrecking bar 600mm THT431242</t>
+          <t>Spark plugs set</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7483,22 +7517,20 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>2860</v>
-      </c>
+          <t>not_required_diesel_engine</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -7506,30 +7538,30 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; one of 9 physical items in PKR 94510 order for chassis lift/clean/suspension work. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+          <t>User correction 2026-05-01: not applicable to the fitted 2H diesel engine; replaced in active baseline by diesel heat/glow plugs.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_spotlight_switch</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7544,17 +7576,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>not_required_allocated_existing_selector</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -7570,29 +7602,25 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_image_2026-03-21_electrical_leftovers|switch_plan_20260417|electrical_master_T5</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Spec ready: order lines RPO-VAC-001A through RPO-VAC-001C define reinforced 10-12 mm vacuum hose working basis, 16-19 mm oil-resistant breather basis, and Toyota/OEM 90923-02079 only if fitted. Complete RPA-009 before payment.</t>
+          <t>Spot lamp control is already allocated to the received Schneider 2-way selector at right dash hole 3 and relay T5; no standalone spotlight switch purchase.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_star_washers</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7607,22 +7635,20 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="n">
-        <v>9870</v>
-      </c>
+          <t>not_required_duplicate_covered_by_millat_kit_d</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>PKR</t>
@@ -7630,87 +7656,400 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_image_2026-03-21_electrical_leftovers|part_fastener_kit_d_millat</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Paid Toolsmart order dated 2026-05-01; hammer and dolly set for aluminium/body panel shaping. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+          <t>Added from the user-provided remaining electrical-items screenshot; grounding hardware for reliable metal-biting earth points. Closed as a standalone duplicate on 2026-05-02: grounding washer stock is registered in Fastener Kit D under paid MTL/Millat orders 38902 and 38903; track receipt against part_fastener_kit_d_millat.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; quantity 2 pairs at PKR 9600 each, four stands total for chassis support. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; one of 9 physical items in PKR 94510 order for chassis lift/clean/suspension work. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>part_mech_vacuum_hose_refresh</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Vacuum hose refresh kit</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Spec ready: order lines RPO-VAC-001A through RPO-VAC-001C define 10-12 mm ID x 2000 mm reinforced vacuum hose, 16-19 mm ID x 1000 mm oil-resistant breather hose, and oil-outlet molded hose only if fitted. Complete RPA-009 before payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Paid Toolsmart order dated 2026-05-01; hammer and dolly set for aluminium/body panel shaping. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>tool_wadfow_pressure_sprayer_wrs1550</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Wadfow Pressure sprayer WRS1550</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>goods</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>pending_delivery</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>ordered_pending_delivery</t>
         </is>
       </c>
-      <c r="I88" s="5" t="n">
+      <c r="I92" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>Toolsmart.pk</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>Paid Toolsmart order dated 2026-05-01; 5L sprayer for water-based degreaser application during chassis/engine/transmission cleaning. Gmail order #TM25493 confirms this line item as part of the PKR 94510 Toolsmart order.</t>
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>part_winch_switch</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Winch switch</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>goods</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>not_required_pending_confirmation</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>not_required_pending_lever_confirmation</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-05-02_parts_review</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Likely controlled from a lever-mounted winch control; no standalone dash switch purchase until lever/control audit proves it missing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M88"/>
+  <autoFilter ref="A1:M93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7721,7 +8060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7729,12 +8068,12 @@
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
   </cols>
@@ -7925,7 +8264,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tool_daraz_75mm_knotted_cup_wire_brush_x2</t>
+          <t>part_wax_and_grease_remover</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7935,13 +8274,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75mm 3 inch steel knotted cup rotary wire brush for angle grinder x2</t>
+          <t>3M Prep Solvent-70 1 gallon / wax and grease remover</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="5" t="n">
-        <v>3896</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>ordered</t>
@@ -7949,7 +8286,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7974,80 +8311,86 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Daraz / Al Rehman Mart (Lahore)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62bcd3dd7207|gmail_order_242365766280938</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00817|user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>part_mech_accessory_belt_set</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>tool_daraz_75mm_knotted_cup_wire_brush_x2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Accessory belt set</t>
+          <t>75mm 3 inch steel knotted cup rotary wire brush for angle grinder x2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>3896</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Al Rehman Mart (Lahore)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>gmail_msg_19de62bcd3dd7207|gmail_order_242365766280938</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_large_power</t>
+          <t>part_mech_accessory_belt_set</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
+          <t>Accessory belt set</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -8089,20 +8432,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_firewall_grommet_set_small_medium</t>
+          <t>part_firewall_grommet_set_large_power</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
+          <t>Additional firewall grommet set IDs 16/20/25 mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -8144,27 +8487,27 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list|docs_wire-heavy-resize-cutlist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>part_mech_air_filter</t>
+          <t>part_firewall_grommet_set_small_medium</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Air filter element</t>
+          <t>Additional firewall grommet set IDs 6/8/10/12 mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8174,22 +8517,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -8199,27 +8542,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_plan_2026-04-22_grommet_size_gap_review|docs_bilal-ganj-master-shopping-list</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>part_android_unit</t>
+          <t>part_mech_air_filter</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Android unit</t>
+          <t>Air filter element</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8229,45 +8572,45 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SehgalMotors.PK</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>part_bed_lining</t>
+          <t>part_android_unit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bed lining</t>
+          <t>Android unit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -8299,30 +8642,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>SehgalMotors.PK</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00318|fj40-00279|fj40-00280|user_update_2026-05-02_dashboard_switch_lcd_update</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>part_bedliner_sprays</t>
+          <t>part_bed_lining</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bedliner sprays</t>
+          <t>Bed lining</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -8354,7 +8697,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -8364,27 +8707,31 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tool_bench_grinder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>part_bedliner_sprays</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bench grinder</t>
+          <t>Bedliner sprays</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8394,52 +8741,52 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>U-POL / Raptor on hand</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|user_shelf_image_2026-05-02_raptor_liner_visible</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>part_body_mount_hardware_kit</t>
+          <t>tool_bench_grinder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Body mount hardware kit bolts sleeves washers</t>
+          <t>Bench grinder</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>spec_ready</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8459,35 +8806,35 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
+          <t>user_seed|akber_khan-00662|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>part_body_mount_shim_pack</t>
+          <t>part_body_mount_hardware_kit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Body mount shim and spacer pack</t>
+          <t>Body mount hardware kit bolts sleeves washers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -8536,13 +8883,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>part_body_mount_rubber_kit</t>
+          <t>part_body_mount_shim_pack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Body-to-chassis mount rubber kit</t>
+          <t>Body mount shim and spacer pack</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -8591,20 +8938,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>part_cable_sleeve_protection</t>
+          <t>part_body_mount_rubber_kit</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
+          <t>Body-to-chassis mount rubber kit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8614,52 +8961,52 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / HAQ ELECTRIC</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
+          <t>user_plan_2026-04-22_tub_off_update|docs_tub-off-refit-execution-plan|data/manual/body_mount_order_release_specs.csv|data/manual/body_mount_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>part_mech_brake_flex_hose_set</t>
+          <t>part_cable_sleeve_protection</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brake flexible hose set front and rear</t>
+          <t>Braided sleeve inventory - 8/10/14/16/20 mm sleeves, 5m lengths received</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>spec_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8669,52 +9016,52 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk / HAQ ELECTRIC</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_seed|akber_khan-00489|fj40-00276|fj40-00282</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tool_cover</t>
+          <t>part_mech_brake_flex_hose_set</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Car cover</t>
+          <t>Brake flexible hose set front and rear</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8724,52 +9071,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Shopify storefront</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
+          <t>user_plan_2026-04-12_engine_bay_review|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>part_carpet</t>
+          <t>tool_cover</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carpet</t>
+          <t>Car cover</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8779,45 +9126,45 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Shopify storefront</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_seed|akber_khan-00793|akber_khan-00805|akber_khan-00806|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>part_mech_clutch_master_slave_refresh</t>
+          <t>part_carpet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Clutch master and slave cylinder refresh kit</t>
+          <t>Carpet</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -8849,7 +9196,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8859,27 +9206,27 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>part_copper_grease</t>
+          <t>part_mech_clutch_master_slave_refresh</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Copper grease for brakes</t>
+          <t>Clutch master and slave cylinder refresh kit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8889,55 +9236,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Pakistan Power Tool</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>part_autohub_diss_apc_cleaner_5l</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>part_copper_grease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DISS (APC) All Purpose Cleaner 5L</t>
+          <t>Copper grease for brakes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" s="5" t="n">
-        <v>4999</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>received</t>
@@ -8945,17 +9286,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -8970,30 +9311,34 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>Pakistan Power Tool</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>part_dielectric_grease</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>part_autohub_diss_apc_cleaner_5l</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dielectric grease</t>
+          <t>DISS (APC) All Purpose Cleaner 5L</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
-        <v>5609</v>
+        <v>4999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -9027,154 +9372,150 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Adenwalla &amp; Sons</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>part_mech_distributor_cap_rotor_tuneup</t>
+          <t>part_dielectric_grease</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Distributor cap rotor and ignition tune-up consumables</t>
+          <t>Dielectric grease</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>5609</v>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Adenwalla &amp; Sons</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_seed|akber_khan-00489|gmail_msg_19d0f6304329edde|gmail_msg_19d9ff896e3406a1|gmail_order_3070231697777489|gmail_package_PK001206015RS|photo_20260424_part_dielectric_grease_aliexpress_order_3070231697777489.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>part_electric_wires</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
+          <t>part_mech_distributor_cap_rotor_tuneup</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
+          <t>Distributor cap rotor and ignition tune-up consumables</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" s="5" t="n">
-        <v>11529</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tool_electrical_test_kit</t>
+          <t>part_electric_wires</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Electrical test kit</t>
+          <t>Electric wire inventory - 4 AWG red/black silicone cable, 1m each (approx 21 mm2)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>8811</v>
+        <v>11529</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9184,22 +9525,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -9209,33 +9550,33 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|user_update_2026-04-22_wiring_built|gmail_msg_19d045e33582292a|gmail_msg_19d3e56a9e4a3991|gmail_order_3070027285627489|gmail_package_PK015187314R|photo_20260424_part_electric_wires_aliexpress_3070027285627489.jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quote_rubber_grommet_set_chat</t>
+          <t>tool_electrical_test_kit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Electrical wire grommet set (200pcs)</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>7860</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Electrical test kit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>8811</v>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>quote</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9245,7 +9586,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9260,47 +9601,53 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>deferred_optional</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>starshop.pk</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>fj40-00276</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00638|gmail_msg_19d146a9c4d6e8c9|gmail_msg_19d7678e0f8b0da0|gmail_msg_19d7b9f19fa4f39f|gmail_order_3070231697877489|photo_20260424_tool_electrical_test_kit_aliexpress_order_3070231697877489.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>part_mech_engine_mount_set</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>quote_rubber_grommet_set_chat</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Engine mount set</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Electrical wire grommet set (200pcs)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>7860</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>quote_only</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9315,30 +9662,30 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>deferred_optional</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>starshop.pk</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>fj40-00276</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>part_mech_engine_oil_filter_service</t>
+          <t>part_mech_engine_mount_set</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Engine oil + oil filter service pack</t>
+          <t>Engine mount set</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -9370,7 +9717,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>next_phase_purchase</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -9387,140 +9734,140 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tool_autohub_engine_detailing_brush_bundle_62191</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
+          <t>part_mech_engine_oil_filter_service</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Engine/detailing brush bundle - tire sidewall brush, large detailing brush, 5 pc detailing brush set</t>
+          <t>Engine oil + oil filter service pack</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>2588</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62cf4907c036|gmail_order_1762191|autohub_order_62191</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>part_epoxy_primer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>tool_autohub_engine_detailing_brush_bundle_62191</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Epoxy primer</t>
+          <t>Engine/detailing brush bundle - tire sidewall brush, large detailing brush, 5 pc detailing brush set</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>2588</v>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>gmail_msg_19de62cf4907c036|gmail_order_1762191|autohub_order_62191</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>part_evaporust_5l</t>
+          <t>part_epoxy_primer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
+          <t>Epoxy primer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9530,52 +9877,56 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_required_duplicate</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>7mart</t>
+          <t>Daraz / ICI Industrial Coatings</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
+          <t>user_seed|akber_khan-00803|user_update_2026-05-02_zinc_rich_epoxy_primer_order</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>part_foam</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>part_evaporust_5l</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Evapo-Rust 5 Litre Heavy Duty Rust Remover</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9585,52 +9936,56 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>7mart</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>user_update_2026-04-22_evaporust_delivered|INV-0031</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>part_mech_fuel_filter</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>part_fastener_kit_a_millat</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
+          <t>Fastener Kit A: Tub-to-chassis mounts (OEM positions) - M10/M12 class 8.8 bolts, matching nuts, flat+spring washers, sleeves</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9640,52 +9995,56 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review</t>
+          <t>gmail_msg_19d9d26f415b48fa|gmail_msg_19d9cd91c8d55038|gmail_msg_19d9ce99ff7c3bab|gmail_msg_19db2d73afb4876e|gmail_msg_19db2d7aa7027a2c|gmail_msg_19dbc4673054004c|gmail_msg_19dbc462741aef46</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>part_mech_fuel_hose_and_clamps</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>part_fastener_kit_b_millat</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fuel-rated rubber hose and clamp kit</t>
+          <t>Fastener Kit B: Body panel/bracket hardware - M6/M8 class 8.8 flange bolts, nyloc nuts, washers</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>spec_ready</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9700,63 +10059,61 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>gmail_msg_19d9d26f415b48fa|gmail_msg_19d9cd91c8d55038|gmail_msg_19d9ce99ff7c3bab|gmail_msg_19db2d73afb4876e|gmail_msg_19db2d7aa7027a2c|gmail_msg_19dbc4673054004c|gmail_msg_19dbc462741aef46</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
+          <t>part_fastener_kit_d_millat</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
+          <t>Fastener Kit D: Grounding hardware - star/serrated washers M6/M8/M10 + cleaned contact points</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" s="5" t="n">
-        <v>3250</v>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -9766,42 +10123,42 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
+          <t>gmail_msg_19d9d26f415b48fa|gmail_msg_19d9cd91c8d55038|gmail_msg_19d9ce99ff7c3bab|gmail_msg_19db2d73afb4876e|gmail_msg_19db2d7aa7027a2c|gmail_msg_19dbc4673054004c|gmail_msg_19dbc462741aef46</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tool_grease_gun</t>
+          <t>part_foam</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Grease gun</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9811,129 +10168,117 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Toolsmart</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
+          <t>user_seed|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>part_h4_ceramic_headlight_connector_high</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>part_mech_fuel_filter</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>H4 ceramic headlight connectors - x4 received</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="n">
-        <v>1350</v>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Auto Xpert Pakistan</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
+          <t>user_plan_2026-04-12_engine_bay_review</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tool_harden_3ton_trolley_jack_730213</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_hidden_diesel_cutoff_switch</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
+          <t>Fuel stop switch / hidden diesel cutoff (needle-type switch)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>54450</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9943,53 +10288,47 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_image_2026-03-21_electrical_leftovers|photo_20260420_221819_gp_YV69fbvA|photo_20260421_194401_gp_1dY3fLdw|user_update_2026-05-02_parts_review</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tool_harden_spring_clamp_set_4in_6pc</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_fuel_hose_and_clamps</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
+          <t>Fuel-rated rubber hose and clamp kit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" s="5" t="n">
-        <v>1200</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -9999,53 +10338,53 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tool_harden_white_rubber_mallet_700g_590437</t>
+          <t>part_autohub_grez_off_hd_degreaser_32oz</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
+          <t>GREZ OFF HD DEGREASER - Spray Nine (32 oz.)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>2380</v>
+        <v>3250</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -10055,7 +10394,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -10065,42 +10404,42 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_update_2026-04-28_autohub_order_62074|user_update_2026-04-29_autohub_cleaners_received|gmail_msg_19dcbfb32e6a25f5|gmail_msg_19dcf4539d6347c5|gmail_order_1762074</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>part_mech_heat_glow_plugs_set</t>
+          <t>tool_grease_gun</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Heat/glow plugs set - diesel 2H</t>
+          <t>Grease gun</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>new_only_planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -10110,107 +10449,117 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>user_seed|akber_khan-00395|akber_khan-00671|fj40-00286|akber_khan-00879</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>part_mech_heater_hose_set</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>part_h4_ceramic_headlight_connector_high</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Heater hose set with clamps</t>
+          <t>H4 ceramic headlight connectors - x4 received</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>1350</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>spec_ready</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Auto Xpert Pakistan</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_image_2026-03-21_electrical_leftovers|gmail_msg_19d0ecbd9da965f4|gmail_order_1599|workbook_parts_row_76_received_y_paid_y|photo_20260424_part_h4_ceramic_headlight_connector_high_autoxpert_order_1599.jpg|user_update_2026-05-01_h4_connectors_received</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>part_hidden_diesel_cutoff_switch</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>part_cavity_wax</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hidden diesel cutoff switch (binary toggle)</t>
+          <t>HB Body U900 cavity wax spray 400ml</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -10220,109 +10569,115 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-04-20_photo_review</t>
+          <t>user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>part_horn_relay</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>tool_harden_3ton_trolley_jack_730213</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Horn relay</t>
+          <t>Harden 3Ton Hydraulic Trolley Jack 730213</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>54450</v>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tool_powerhouse_ingco_wb30501_wire_cup_brush_x3</t>
+          <t>tool_harden_spring_clamp_set_4in_6pc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INGCO WB30501 Wire Cup Brush x3</t>
+          <t>Harden 6Pc x 4 inch Spring Clamp Set</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>1065</v>
+        <v>1200</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -10356,19 +10711,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Powerhouse Express</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>gmail_msg_19de632df983464c|gmail_order_26242</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
+          <t>tool_harden_white_rubber_mallet_700g_590437</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10378,12 +10733,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
+          <t>Harden White Rubber Mallet with Fiberglass Handle 700g 590437</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>2050</v>
+        <v>2380</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -10429,24 +10784,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>part_ironman_front_dampers_separate_shipment</t>
+          <t>part_suspension_wooden_cribbing_blocks</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
+          <t>Hardwood cribbing / wooden support blocks for suspension replacement - 12 piece working set</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -10456,63 +10811,57 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>local timber / hardware supplier</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
+          <t>user_update_2026-05-02_suspension_wooden_blocks</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>part_ironman_foamcell_suspension_kit</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_heat_glow_plugs_set</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
+          <t>Heat/glow plugs set - diesel 2H</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>575000</v>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>new_only_planned</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -10522,58 +10871,52 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ironman 4x4 supplier</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>part_daraz_jubilee_hose_clip_assortment_30pc</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
+          <t>part_mech_heater_hose_set</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jubilee hose clip assortment - 10 pc fuel line/diesel/petrol/coolant clamp packs x3</t>
+          <t>Heater hose set with clamps</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>2390</v>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -10583,47 +10926,51 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Daraz / Gravax corporation</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62bcdb1080ff|gmail_order_242365766580938</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>part_metal_protection</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>part_primer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Metal protection and restoration products</t>
+          <t>Hi-Build Zinc Rich Epoxy Primer EC 11 two-pack set</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -10633,119 +10980,113 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Daraz / ICI Industrial Coatings</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00397|akber_khan-00701</t>
+          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819|user_update_2026-05-02_zinc_rich_epoxy_primer_order</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>part_battery_purchase</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
+          <t>part_horn_relay</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New battery purchase - installed</t>
+          <t>Horn relay</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>installed</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>not_required_duplicate</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Ghazi Road</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>akber_khan-00753</t>
+          <t>user_image_2026-03-21_electrical_leftovers|electrical_master_T3|user_update_2026-05-02_parts_review</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+          <t>tool_powerhouse_ingco_wb30501_wire_cup_brush_x3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
+          <t>INGCO WB30501 Wire Cup Brush x3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>2188</v>
+        <v>1065</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -10755,7 +11096,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -10765,97 +11106,107 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Daraz</t>
+          <t>Powerhouse Express</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg|gmail_msg_19dd86b5fbb89675|gmail_delivery_241938794080938</t>
+          <t>gmail_msg_19de632df983464c|gmail_order_26242</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>part_piano_hinge</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>tool_ingco_dead_blow_mallet_2lb_hdbm08028</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Piano hinge</t>
+          <t>Ingco Dead blow mallet 2lb HDBM08028</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>2050</v>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Toolsmart.pk</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>user_seed</t>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>part_power_steering_upgrade</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>part_ironman_front_dampers_separate_shipment</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Power steering upgrade</t>
+          <t>Ironman Foamcell front damper pair - separate shipment (24635FE x2)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -10865,162 +11216,178 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>researching</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
+          <t>user_update_2026-05-01_front_dampers_separate_shipment|image_2026-05-01_ironman_foamcell_parts_list|ironman_24635FE_front_reference</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>part_primer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>part_ironman_foamcell_suspension_kit</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Ironman Foamcell suspension kit - main shipment (front dampers separate)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" s="5" t="n">
+        <v>575000</v>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ironman 4x4 supplier</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00798|akber_khan-00800|akber_khan-00819</t>
+          <t>user_update_2026-05-01_ironman_foamcell_order|image_2026-05-01_ironman_foamcell_parts_list</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>part_mech_radiator_cap</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>part_daraz_jubilee_hose_clip_assortment_30pc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Jubilee hose clip assortment - 10 pc fuel line/diesel/petrol/coolant clamp packs x3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>2390</v>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz / Gravax corporation</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
+          <t>gmail_msg_19de62bcdb1080ff|gmail_order_242365766580938</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>part_mech_radiator_hose_set</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>part_metal_protection</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Radiator hose set upper plus lower with clamps</t>
+          <t>Metal protection and restoration products</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>spec_ready</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -11040,152 +11407,164 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>not_required_covered_by_epoxy_wax</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_seed|akber_khan-00397|akber_khan-00701|user_update_2026-05-02_zinc_rich_epoxy_primer_order|user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>part_rear_axle_hard_brake_lines</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>part_battery_purchase</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rear axle hard brake lines and fittings</t>
+          <t>New battery purchase - installed</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>20000</v>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>installed</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>spec_needed_before_order</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Ghazi Road</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>BR-REAR-002|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
+          <t>akber_khan-00753</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>part_rear_brake_line_cable_clips</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>part_nylon_fiber_wool_polishing_disc_sets_2x</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rear brake line clips and parking-brake cable retainers</t>
+          <t>Nylon fiber polishing disc and wool buffing polishing disc set (3pcs) plus drill adapter and grinder nut for metals x2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>2188</v>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>spec_needed_before_order</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>Daraz</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>BR-REAR-006|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
+          <t>user_update_2026-04-24_wirecup_schedule_parts_update|gmail_msg_19dbbce97316517e|gmail_order_241938794080938|photo_20260424_part_nylon_fiber_wool_polishing_disc_sets_2x_daraz_241938794080938.jpg|gmail_msg_19dd86b5fbb89675|gmail_delivery_241938794080938</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>part_rear_brake_shoes_hardware</t>
+          <t>part_piano_hinge</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rear brake shoes and spring hardware set</t>
+          <t>Piano hinge</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -11195,22 +11574,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>inspect_then_buy</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -11220,27 +11599,27 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>BR-REAR-005|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
+          <t>user_seed</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>part_rear_center_brake_flex_hose</t>
+          <t>part_power_steering_upgrade</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rear center frame-to-axle flexible brake hose</t>
+          <t>Power steering upgrade</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -11250,7 +11629,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -11260,12 +11639,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>spec_needed_before_order</t>
+          <t>researching</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -11275,20 +11654,20 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>BR-REAR-003|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
+          <t>user_seed|fj40-00006|fj40-00263|akber_khan-00346|akber_khan-00858</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>part_rear_parking_brake_cable_set</t>
+          <t>part_mech_radiator_cap</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rear parking brake cable set with clips and equalizer hardware</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -11320,7 +11699,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>spec_needed_before_order</t>
+          <t>purchase_ready</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -11330,27 +11709,27 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>BR-REAR-001|20260501_194305_gp_EllBGvXA|20260501_194322_gp_XuRtjN4w</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>part_rear_wheel_cylinders_pair</t>
+          <t>part_mech_radiator_hose_set</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rear wheel cylinders pair with bleed screws</t>
+          <t>Radiator hose set upper plus lower with clamps</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>spec_ready</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -11360,7 +11739,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -11375,7 +11754,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>inspect_then_buy</t>
+          <t>spec_ready_release_hold</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -11385,31 +11764,27 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>BR-REAR-004|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>part_rubber_grommet_set</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
+          <t>part_rear_axle_hard_brake_lines</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rubber grommet set</t>
+          <t>Rear axle hard brake lines and fittings</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -11419,167 +11794,155 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
+          <t>BR-REAR-002|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tool_daraz_safety_goggles_cleanup</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
+          <t>part_rear_brake_line_cable_clips</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Safety goggles / protective glasses for grinding and cleaning</t>
+          <t>Rear brake line clips and parking-brake cable retainers</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>764</v>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Daraz / Reliable_Shop</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>gmail_msg_19de62bcddc3ff3a|gmail_order_242365766080938</t>
+          <t>BR-REAR-006|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>part_seam_sealer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
+          <t>part_rear_brake_shoes_hardware</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seam sealer</t>
+          <t>Rear brake shoes and spring hardware set</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>7696</v>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>inspect_then_buy</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg</t>
+          <t>BR-REAR-005|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>part_self_etching_primer</t>
+          <t>part_rear_center_brake_flex_hose</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Self etching primer</t>
+          <t>Rear center frame-to-axle flexible brake hose</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -11611,7 +11974,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -11621,20 +11984,20 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803</t>
+          <t>BR-REAR-003|20260501_194305_gp_EllBGvXA|20260501_194313_gp_lfUqLibA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>part_sound_dampening_sheets</t>
+          <t>part_rear_parking_brake_cable_set</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sound dampening sheets</t>
+          <t>Rear parking brake cable set with clips and equalizer hardware</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -11666,7 +12029,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>deferred_until_body_closed</t>
+          <t>spec_needed_before_order</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -11676,27 +12039,27 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
+          <t>BR-REAR-001|20260501_194305_gp_EllBGvXA|20260501_194322_gp_XuRtjN4w</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>part_mech_spark_plugs_set</t>
+          <t>part_rear_wheel_cylinders_pair</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spark plugs set</t>
+          <t>Rear wheel cylinders pair with bleed screws</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -11706,7 +12069,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -11716,12 +12079,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>not_ordered</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>not_required_diesel_engine</t>
+          <t>inspect_then_buy</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -11731,20 +12094,24 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
+          <t>BR-REAR-004|20260501_194322_gp_XuRtjN4w|20260324_004906</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_medium</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>part_rubber_grommet_set</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
+          <t>Rubber grommet set</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -11781,42 +12148,48 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>AliExpress</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00489|akber_khan-00497|fj40-00276|fj40-00282|user_update_2026-04-22_grommet_received|user_update_2026-05-01_grommet_image_wrong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_large</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>tool_daraz_safety_goggles_cleanup</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
+          <t>Safety goggles / protective glasses for grinding and cleaning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>764</v>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -11826,52 +12199,58 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>Daraz / Reliable_Shop</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>gmail_msg_19de62bcddc3ff3a|gmail_order_242365766080938</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>part_split_conduit_braided_sleeve_small</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>part_seam_sealer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
+          <t>Seam sealer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>7696</v>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -11881,42 +12260,46 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>pending_delivery</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>ordered_pending_delivery</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>electronicsstore.pk / workbook inventory</t>
+          <t>Autohub</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803|akber_khan-00820|gmail_msg_19d0ef66d4eacdee|gmail_msg_19d48a1d197405a3|gmail_order_1761310|photo_20260424_part_seam_sealer_autohub_order_1761310.jpg|user_update_2026-05-02_autohub_prep_solvent_cavity_wax_order</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>part_spotlight_switch</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>part_self_etching_primer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spotlight switch</t>
+          <t>Self etching primer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -11926,7 +12309,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -11936,12 +12319,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>not_required_with_epoxy</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -11951,20 +12334,20 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00803|user_update_2026-05-02_zinc_rich_epoxy_primer_order</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>part_star_washers</t>
+          <t>part_sound_dampening_sheets</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Star washers (bite into metal)</t>
+          <t>Sound dampening sheets</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -11996,7 +12379,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>purchase_ready</t>
+          <t>deferred_until_body_closed</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -12006,27 +12389,27 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+          <t>user_seed|akber_khan-00430|akber_khan-00798|akber_khan-00803</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tool_tap_set</t>
+          <t>part_mech_spark_plugs_set</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tap set</t>
+          <t>Spark plugs set</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -12036,45 +12419,45 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>open</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>received</t>
+          <t>not_required_diesel_engine</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_diesel_correction</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>part_mech_thermostat_gasket</t>
+          <t>part_split_conduit_braided_sleeve_medium</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thermostat plus gasket</t>
+          <t>Split conduit / braided sleeve inventory - 14/16 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -12091,12 +12474,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -12111,25 +12494,25 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>tool_torque_wrench</t>
+          <t>part_split_conduit_braided_sleeve_large</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Torque wrench</t>
+          <t>Split conduit / braided sleeve inventory - 20 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -12146,12 +12529,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>registered_needs_confirmation</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -12166,48 +12549,42 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ToolsMart.pk</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00395</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_split_conduit_braided_sleeve_small</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+          <t>Split conduit / braided sleeve inventory - 8/10 mm, 5m lengths</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>19200</v>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -12217,53 +12594,47 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>electronicsstore.pk / workbook inventory</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_image_2026-03-21_electrical_leftovers</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tool_total_wrecking_bar_600mm_tht431242</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_spotlight_switch</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Total Wrecking bar 600mm THT431242</t>
+          <t>Spotlight switch</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>2860</v>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12273,47 +12644,47 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>not_required_allocated_existing_selector</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_image_2026-03-21_electrical_leftovers|switch_plan_20260417|electrical_master_T5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>part_mech_vacuum_hose_refresh</t>
+          <t>part_star_washers</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Vacuum hose refresh kit</t>
+          <t>Star washers (bite into metal)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>spec_ready</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -12328,169 +12699,157 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>spec_ready_release_hold</t>
+          <t>not_required_duplicate_covered_by_millat_kit_d</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>TBD (confirm)</t>
+          <t>MTL Parts</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+          <t>user_image_2026-03-21_electrical_leftovers|part_fastener_kit_d_millat</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>tool_tap_set</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+          <t>Tap set</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>9870</v>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_seed|akber_khan-00663|akber_khan-00664</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>part_mech_thermostat_gasket</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wadfow Pressure sprayer WRS1550</t>
+          <t>Thermostat plus gasket</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>2500</v>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>ordered_pending_delivery</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Toolsmart.pk</t>
+          <t>TBD (confirm)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-04-20_photo_review</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>part_wax_and_grease_remover</t>
+          <t>tool_torque_wrench</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wax and grease remover</t>
+          <t>Torque wrench</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>received</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -12500,92 +12859,391 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>registered_needs_confirmation</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>not_paid</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>not_ordered</t>
+          <t>received</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>next_phase_purchase</t>
+          <t>received</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Autohub</t>
+          <t>ToolsMart.pk</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>user_seed|akber_khan-00803|akber_khan-00817</t>
+          <t>user_seed|akber_khan-00395</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>tool_total_jack_stands_3ton_thjs0301_2pairs</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Total Jack stand 3Ton THJS0301 - 2 pairs</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>19200</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>tool_total_wrecking_bar_600mm_tht431242</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Total Wrecking bar 600mm THT431242</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>part_mech_vacuum_hose_refresh</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Vacuum hose refresh kit</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>spec_ready</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>not_paid</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>not_ordered</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>spec_ready_release_hold</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>TBD (confirm)</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>user_plan_2026-04-12_engine_bay_review|user_update_2026-05-01_engine_hose_spec|data/manual/replacement_pipe_order_release_specs.csv|data/manual/replacement_pipe_release_actions.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>tool_wadfow_body_fender_hammer_set_whz1d07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Wadfow 7 Pcs Body And Fender Hammer Set WHZ1D07</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>9870</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>tool_wadfow_pressure_sprayer_wrs1550</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Wadfow Pressure sprayer WRS1550</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>pending_delivery</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>ordered_pending_delivery</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Toolsmart.pk</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>user_update_2026-05-01_toolsmart_chassis_lift_clean_suspension_order|gmail_msg_19de060f62c307f7|gmail_order_TM25493</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>part_winch_switch</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr">
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
         <is>
           <t>Winch switch</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>not_paid</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>deferred_optional</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>not_required_pending_confirmation</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>not_required_pending_lever_confirmation</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>TBD (confirm)</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>user_image_2026-03-21_electrical_leftovers</t>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>user_image_2026-03-21_electrical_leftovers|user_update_2026-05-02_parts_review</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M85"/>
+  <autoFilter ref="A1:M90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
